--- a/data-room/07-financials/FINANCIAL_MODEL.xlsx
+++ b/data-room/07-financials/FINANCIAL_MODEL.xlsx
@@ -9,13 +9,14 @@
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Hypotheses" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Unit Economics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Pipeline" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Actuals" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Budget (Base)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Scenarios" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Cap Table" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Use of Funds" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Scenarios (Deck)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Unit Economics" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Pipeline" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Actuals" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Budget (Base)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Scenarios (Bottom-Up)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Cap Table" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Use of Funds" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,8 +26,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0;[RED]-#,##0"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="#,##0;[RED]-#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="5">
@@ -98,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -114,27 +115,32 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -223,7 +229,167 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Base case — Revenue vs. Cash balance</a:t>
+              <a:t>Revenue projected in three scenarios (US$M/year) — from the pitch deck</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Scenarios (Deck)'!B7</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Scenarios (Deck)'!$A$8:$A$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Scenarios (Deck)'!$B$8:$B$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Scenarios (Deck)'!C7</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Scenarios (Deck)'!$A$8:$A$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Scenarios (Deck)'!$C$8:$C$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Scenarios (Deck)'!D7</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Scenarios (Deck)'!$A$8:$A$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Scenarios (Deck)'!$D$8:$D$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>US$ millions/year</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Bottom-up build — Revenue vs. Cash balance (US$)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1255,7 +1421,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>R$</a:t>
+                  <a:t>US$</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1275,7 +1441,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -1287,7 +1453,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>18-month total revenue by scenario</a:t>
+              <a:t>18-month total revenue by scenario (bottom-up build, US$)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1307,12 +1473,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Scenarios'!$A$13:$A$15</f>
+              <f>'Scenarios (Bottom-Up)'!$A$13:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Scenarios'!$C$13:$C$15</f>
+              <f>'Scenarios (Bottom-Up)'!$C$13:$C$15</f>
             </numRef>
           </val>
         </ser>
@@ -1347,7 +1513,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>R$</a:t>
+                  <a:t>US$</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -1368,6 +1534,33 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1394,7 +1587,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1710,7 +1903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1726,7 +1919,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AgrosTech — Financial Model v1.0</t>
+          <t>AgrosTech — Financial Model v2.0</t>
         </is>
       </c>
     </row>
@@ -1754,40 +1947,183 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>• This model uses the R$4/ha/year subscription (Passaporte de Crédito Rural) + one-off survey services pricing confirmed by the founder on 2026-09-24.</t>
+          <t>• v2.0: reconciled against the founder's pitch deck (AgrosTech_Pitch_Narrativo.pdf, 2026-09-24). USD is now the primary currency throughout (the SAFE is a US-dollar instrument) — R$ shown as a secondary reference at an assumed ~R$5.00/US$1.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>• It intentionally does NOT use the older R$35-120/ha drone-mission pricing in knowledge-base/PRICING_MODEL.md — that belonged to a prior services-only version of the business model.</t>
+          <t>• Core confirmed numbers: US$0.80/ha/year subscription (Passaporte de Crédito Rural) + one-off survey services; US$600,000 raise at a US$4,000,000 post-money cap (15%), 4yr vesting/1yr cliff.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>• Tabs: Hypotheses -&gt; Unit Economics -&gt; Pipeline -&gt; Actuals -&gt; Budget (18mo) -&gt; Scenarios (Bull/Base/Bear) -&gt; Cap Table -&gt; Use of Funds.</t>
+          <t>• It intentionally does NOT use the older R$35-120/ha drone-mission pricing in knowledge-base/PRICING_MODEL.md — that belonged to a prior services-only version of the business model.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>• Scenario logic: Budget tab computes the BASE case directly. Scenarios tab applies bull/base/bear multipliers (cells B4:B6 on that tab) to the base case's hectare-growth and survey-volume drivers, then recomputes revenue/burn/runway for each.</t>
+          <t>• Tabs: Hypotheses -&gt; 'Scenarios (Deck)' [the OFFICIAL forecast, taken directly from the pitch deck] -&gt; Unit Economics -&gt; Pipeline -&gt; Actuals -&gt; Budget (18mo) [a supporting bottom-up build, see its own note] -&gt; Scenarios (Bottom-Up) -&gt; Cap Table -&gt; Use of Funds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>• 'Scenarios (Deck)' is the number to lead with in investor conversations — it's the founder's own stated forecast. The 'Budget (Base)' / 'Scenarios (Bottom-Up)' tabs are an independent monthly build from named pipeline + cost assumptions, useful as a sanity check and for burn/runway planning, but on a different time basis (rolling 18mo from raise-close vs. calendar year) — the two are not expected to match exactly, and that's noted on both tabs.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A10:H10"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A6:H6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Use of Funds</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Mirrors 04-investment-documents/USE_OF_FUNDS.md. Percentages confirmed directly on the pitch deck's 'O Pedido' slide — goal: get 1.5 million hectares 'in sight' by 2028.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total raise (US$)</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>% of raise (confirmed — deck)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>US$</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Dados e IA (Data &amp; AI — the M1/M2/M3 model stack)</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C8" s="17">
+        <f>B8*$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Vendas institucionais (Institutional sales — banks, cooperatives, credit desks)</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C9" s="17">
+        <f>B9*$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Operações e reserva (Operations &amp; reserve)</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C10" s="17">
+        <f>B10*$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Integrações Bacen e segurança (Bacen integrations &amp; security)</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C11" s="17">
+        <f>B11*$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B12" s="28">
+        <f>SUM(B8:B11)</f>
+        <v/>
+      </c>
+      <c r="C12" s="25">
+        <f>SUM(C8:C11)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:C3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1799,7 +2135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1873,17 +2209,17 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>R$ 4.00/ha/year</t>
+          <t>US$ 0.80/ha/year (≈R$4.00)</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>R$ 4.00/ha/year (unchanged)</t>
+          <t>US$ 0.80/ha/year (unchanged)</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>R$ 3.20/ha/year (-20%, price pressure)</t>
+          <t>US$ 0.64/ha/year (-20%, price pressure)</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -1893,7 +2229,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Founder-confirmed core price point</t>
+          <t>Confirmed by founder and by the deck's 'O Mercado' slide</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2344,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Pipeline conversion — Thales (30,000 ha cacao, Bahia)</t>
+          <t>Pipeline conversion — Thales (~30,000 ha cacao, Bahia, 200+ producers) + unnamed global trading/barter manager (deck's combined figure: 35,000 ha)</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -2033,7 +2369,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Consultant relationship, not direct producer — conversion probability especially uncertain</t>
+          <t>Consultant relationship, not direct producer — conversion probability especially uncertain; see Pipeline tab for the two-contact reconciliation</t>
         </is>
       </c>
     </row>
@@ -2209,6 +2545,41 @@
       <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Not yet provided</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Base-case driver for the deck's official 2027-2029 forecast</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>~8 cooperativas (cooperative-scale accounts) by 2028, at US$0.80/ha</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>More/larger accounts, faster</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Fewer/smaller accounts, slower</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Low — deck's own stated assumption, not independently modeled bottom-up</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Directly from the deck's revenue-scenario slide footnote; see 'Scenarios (Deck)' tab</t>
         </is>
       </c>
     </row>
@@ -2227,6 +2598,180 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Scenarios — Official Forecast (from the Pitch Deck)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>This is the founder's own stated forecast, taken verbatim from the pitch deck's 'Receita projetada em três cenários' slide (AgrosTech_Pitch_Narrativo.pdf, 2026-09-24). LEAD WITH THIS TAB in investor conversations — the 'Budget (Base)' / 'Scenarios (Bottom-Up)' tabs are a separate, independently-built bottom-up model on a different time basis (rolling 18mo from raise-close), kept as a supporting sanity check, not a competing forecast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Basis (per the deck's own footnote)</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>US$ 0.80/ha and ~8 cooperativas (cooperative-scale accounts) in 2028. Projections, not results.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Pessimista (US$M)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Base (US$M)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Otimista (US$M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>2028</v>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>4.56</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Implied CAGR 2027→2029 (Base)</t>
+        </is>
+      </c>
+      <c r="B12" s="9">
+        <f>(C10/C8)^(1/2)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Cross-check vs. the 36-month (~2029) target on the deck's market slide</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Deck's stated 36-month target (US$M, from 'O Mercado' slide)</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>This tab's 2029 Base case (US$M)</t>
+        </is>
+      </c>
+      <c r="B16" s="10">
+        <f>C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="B17" s="10">
+        <f>B16-B15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>The 36-month target (US$3M, stated on the market-sizing slide) and the 2029 Base-case revenue projection (US$3.50M, stated on the scenarios slide) are close but not identical — both are the founder's own numbers from two different slides of the same deck, not a discrepancy this data room introduced. Worth a quick founder gut-check on which framing to lead with (a single target figure vs. the full scenario table), but not a red flag requiring reconciliation.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B5:F5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2244,7 +2789,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Built fresh for the R$4/ha/year subscription + survey-services model. Does not reuse knowledge-base/UNIT_ECONOMICS.md, which priced full drone missions per hectare under a different business model.</t>
+          <t>Built fresh for the US$0.80/ha/year (≈R$4) subscription + survey-services model, confirmed by the founder and the pitch deck. Does not reuse knowledge-base/UNIT_ECONOMICS.md, which priced full drone missions per hectare under a different business model.</t>
         </is>
       </c>
     </row>
@@ -2258,12 +2803,11 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Price per ha/year</t>
-        </is>
-      </c>
-      <c r="B6" s="7">
-        <f>4</f>
-        <v/>
+          <t>Price per ha/year (US$)</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
@@ -2272,7 +2816,7 @@
           <t>Gross margin %  [CONFIRM]</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="12" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2282,7 +2826,7 @@
           <t>Gross profit per ha/year</t>
         </is>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="11">
         <f>B6*B7</f>
         <v/>
       </c>
@@ -2293,7 +2837,7 @@
           <t>Avg. hectares per customer  [CONFIRM]</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="13" t="n">
         <v>1500</v>
       </c>
     </row>
@@ -2303,7 +2847,7 @@
           <t>Annual revenue per customer</t>
         </is>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="11">
         <f>B6*B9</f>
         <v/>
       </c>
@@ -2314,7 +2858,7 @@
           <t>Annual gross profit per customer</t>
         </is>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="11">
         <f>B7*B10</f>
         <v/>
       </c>
@@ -2325,7 +2869,7 @@
           <t>Monthly churn  [CONFIRM]</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="12" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -2335,7 +2879,7 @@
           <t>Implied avg. customer lifetime (months)</t>
         </is>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="14">
         <f>1/B12</f>
         <v/>
       </c>
@@ -2346,7 +2890,7 @@
           <t>LTV (gross profit basis)</t>
         </is>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="11">
         <f>B11/12*B13</f>
         <v/>
       </c>
@@ -2361,11 +2905,11 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Avg. fee per survey  [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="n">
-        <v>15000</v>
+          <t>Avg. fee per survey (US$)  [CONFIRM]</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n">
+        <v>3000</v>
       </c>
     </row>
     <row r="18">
@@ -2374,7 +2918,7 @@
           <t>Gross margin %  [CONFIRM]</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n">
+      <c r="B18" s="12" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -2384,7 +2928,7 @@
           <t>Gross profit per survey</t>
         </is>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="11">
         <f>B17*B18</f>
         <v/>
       </c>
@@ -2402,7 +2946,7 @@
           <t>Estimated CAC per subscription customer  [CONFIRM]</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>[CONFIRM — no paid acquisition spend to date; pipeline so far is founder-led relationship sales (Coplacana, Thales)]</t>
         </is>
@@ -2420,13 +2964,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2448,7 +2992,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Named accounts confirmed by founder 2026-09-24. Stage/probability/timing are [CONFIRM] placeholders feeding the Budget tab's ramp.</t>
+          <t>Named accounts confirmed by founder 2026-09-24 and the pitch deck's traction slide. The deck's combined '35,000 ha prospected' figure is split below into two contacts (consultant + trading/barter manager) — see 06-customers/SALES_PIPELINE.md for the full reconciliation. Stage/probability/timing are [CONFIRM] placeholders feeding the Budget tab's ramp.</t>
         </is>
       </c>
     </row>
@@ -2485,7 +3029,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Annual subscription value (ha x R$4)</t>
+          <t>Annual subscription value (ha x US$0.80)</t>
         </is>
       </c>
     </row>
@@ -2495,37 +3039,37 @@
           <t>Coplacana</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cooperative</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>[CONFIRM]</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>[CONFIRM]</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>[CONFIRM]</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>[CONFIRM]</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="n"/>
+      <c r="G6" s="17" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Thales — cacao consultant, Bahia</t>
+          <t>Thales — cacao consultant, Bahia, 200+ producers</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2536,270 +3080,109 @@
       <c r="C7" t="n">
         <v>30000</v>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>[CONFIRM]</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>[CONFIRM — 20% used as base case, see Hypotheses]</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>[CONFIRM]</t>
         </is>
       </c>
-      <c r="G7" s="13">
-        <f>C7*4</f>
+      <c r="G7" s="17">
+        <f>C7*0.8</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>[Global trading/barter manager — unnamed, per deck]</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Consultant / channel</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>[CONFIRM — deck implies ~5,000 ha to reach the combined 35,000 ha total]</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>[CONFIRM]</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>[CONFIRM]</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>[CONFIRM]</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>[Other pipeline accounts]</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>[CONFIRM]</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>[CONFIRM]</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>[CONFIRM]</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>[CONFIRM]</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>[CONFIRM]</t>
         </is>
       </c>
-      <c r="G8" s="13" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>Total (named pipeline, illustrative)</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="n"/>
-      <c r="C9" s="16">
-        <f>SUM(C6:C8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="17">
-        <f>SUM(G6:G8)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Actuals to Date</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Revenue delivered/paid to date, per founder correction: the CAR/SICAR georeferencing survey (client Fabio) and the 35ha weed-stress scan are the two confirmed engagements. Amounts are [CONFIRM] pending founder figures.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Client</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Engagement</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Amount (R$)</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>[CONFIRM date]</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Fabio</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CAR/SICAR georeferencing survey</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>One-off survey</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Delivered &amp; paid</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>[CONFIRM date]</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>[CONFIRM client]</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>35 ha weed-stress scan (10 ha affected)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>One-off survey</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>Total revenue to date</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="17">
-        <f>SUM(E6:E7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="15" t="n"/>
+      <c r="G9" s="17" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>Cash &amp; burn to date  [CONFIRM]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Cash in bank today</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Avg. monthly burn to date</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Runway at current burn (months)</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
+          <t>Total (named pipeline, illustrative)</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="n"/>
+      <c r="C10" s="20">
+        <f>SUM(C6:C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="21">
+        <f>SUM(G6:G9)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2812,6 +3195,213 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Actuals to Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Revenue delivered/paid to date. Per the founder and the deck's traction slide: the 220ha CAR/SICAR georeferencing survey (Minas Gerais, likely = client 'Fabio' — link marked [CONFIRM]) and the 35ha weed-stress scan are the two confirmed engagements. Amounts are [CONFIRM] pending founder figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Engagement</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Hectares</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Amount (US$)</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>[CONFIRM date]</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Fabio [CONFIRM link to deck's 220ha project]</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CAR/SICAR georeferencing survey, Minas Gerais</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>One-off survey</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220</v>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>[CONFIRM]</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Delivered &amp; paid — generated retention and scope renegotiation (per deck)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>[CONFIRM date]</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>[CONFIRM client]</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>35 ha weed-stress scan (10 ha affected)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>One-off survey</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>35</v>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>[CONFIRM]</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>[CONFIRM]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>Total revenue to date</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="n"/>
+      <c r="C8" s="19" t="n"/>
+      <c r="D8" s="19" t="n"/>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="21">
+        <f>SUM(F6:F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="19" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Cash &amp; burn to date  [CONFIRM]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cash in bank today</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>[CONFIRM]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Avg. monthly burn to date</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>[CONFIRM]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Runway at current burn (months)</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>[CONFIRM]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2844,14 +3434,14 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>18-Month Budget — Base Case</t>
+          <t>18-Month Budget — Bottom-Up Build (Supporting)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>All driver assumptions live in green cells on row 5-13, columns C onward. Change these, not the formula rows, to adjust the model. Months are relative (M1 = first full month post-close).</t>
+          <t>SUPPORTING MODEL, not the official forecast — see the 'Scenarios (Deck)' tab for that. This is an independent bottom-up build (named pipeline x unit economics x cost assumptions), useful for burn/runway planning. Figures are in US$. All driver assumptions live in green cells. Change these, not the formula rows, to adjust the model. Months are relative (M1 = first full month post-close), which is a different time basis than the deck's calendar-year scenarios — the two are not expected to match exactly.</t>
         </is>
       </c>
     </row>
@@ -2861,92 +3451,92 @@
           <t>Driver / Line item</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="E5" s="19" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>M6</t>
         </is>
       </c>
-      <c r="H5" s="19" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t>M7</t>
         </is>
       </c>
-      <c r="I5" s="19" t="inlineStr">
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t>M8</t>
         </is>
       </c>
-      <c r="J5" s="19" t="inlineStr">
+      <c r="J5" s="23" t="inlineStr">
         <is>
           <t>M9</t>
         </is>
       </c>
-      <c r="K5" s="19" t="inlineStr">
+      <c r="K5" s="23" t="inlineStr">
         <is>
           <t>M10</t>
         </is>
       </c>
-      <c r="L5" s="19" t="inlineStr">
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t>M11</t>
         </is>
       </c>
-      <c r="M5" s="19" t="inlineStr">
+      <c r="M5" s="23" t="inlineStr">
         <is>
           <t>M12</t>
         </is>
       </c>
-      <c r="N5" s="19" t="inlineStr">
+      <c r="N5" s="23" t="inlineStr">
         <is>
           <t>M13</t>
         </is>
       </c>
-      <c r="O5" s="19" t="inlineStr">
+      <c r="O5" s="23" t="inlineStr">
         <is>
           <t>M14</t>
         </is>
       </c>
-      <c r="P5" s="19" t="inlineStr">
+      <c r="P5" s="23" t="inlineStr">
         <is>
           <t>M15</t>
         </is>
       </c>
-      <c r="Q5" s="19" t="inlineStr">
+      <c r="Q5" s="23" t="inlineStr">
         <is>
           <t>M16</t>
         </is>
       </c>
-      <c r="R5" s="19" t="inlineStr">
+      <c r="R5" s="23" t="inlineStr">
         <is>
           <t>M17</t>
         </is>
       </c>
-      <c r="S5" s="19" t="inlineStr">
+      <c r="S5" s="23" t="inlineStr">
         <is>
           <t>M18</t>
         </is>
@@ -2958,7 +3548,7 @@
           <t>Cumulative hectares under subscription</t>
         </is>
       </c>
-      <c r="B6" s="20" t="n">
+      <c r="B6" s="24" t="n">
         <v>500</v>
       </c>
       <c r="C6">
@@ -3036,75 +3626,75 @@
           <t>New surveys delivered this month  [CONFIRM ramp]</t>
         </is>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="24">
         <f>ROUND(2+(1-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="24">
         <f>ROUND(2+(2-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="24">
         <f>ROUND(2+(3-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="24">
         <f>ROUND(2+(4-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="24">
         <f>ROUND(2+(5-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="24">
         <f>ROUND(2+(6-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="24">
         <f>ROUND(2+(7-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="24">
         <f>ROUND(2+(8-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="J7" s="20">
+      <c r="J7" s="24">
         <f>ROUND(2+(9-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="K7" s="20">
+      <c r="K7" s="24">
         <f>ROUND(2+(10-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="L7" s="20">
+      <c r="L7" s="24">
         <f>ROUND(2+(11-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="M7" s="20">
+      <c r="M7" s="24">
         <f>ROUND(2+(12-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="N7" s="20">
+      <c r="N7" s="24">
         <f>ROUND(2+(13-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="O7" s="20">
+      <c r="O7" s="24">
         <f>ROUND(2+(14-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="P7" s="20">
+      <c r="P7" s="24">
         <f>ROUND(2+(15-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="Q7" s="20">
+      <c r="Q7" s="24">
         <f>ROUND(2+(16-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="R7" s="20">
+      <c r="R7" s="24">
         <f>ROUND(2+(17-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="S7" s="20">
+      <c r="S7" s="24">
         <f>ROUND(2+(18-1)*0.24,0)</f>
         <v/>
       </c>
@@ -3119,78 +3709,78 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Subscription revenue (monthly recognition of R$4/ha/yr)</t>
-        </is>
-      </c>
-      <c r="B10" s="13">
+          <t>Subscription revenue (monthly recognition of US$0.80/ha/yr)</t>
+        </is>
+      </c>
+      <c r="B10" s="17">
         <f>B6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="17">
         <f>C6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="17">
         <f>D6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="17">
         <f>E6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="17">
         <f>F6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="17">
         <f>G6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="17">
         <f>H6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="17">
         <f>I6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="17">
         <f>J6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="K10" s="13">
+      <c r="K10" s="17">
         <f>K6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="17">
         <f>L6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="17">
         <f>M6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="N10" s="13">
+      <c r="N10" s="17">
         <f>N6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="O10" s="13">
+      <c r="O10" s="17">
         <f>O6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="P10" s="13">
+      <c r="P10" s="17">
         <f>P6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="Q10" s="13">
+      <c r="Q10" s="17">
         <f>Q6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="R10" s="13">
+      <c r="R10" s="17">
         <f>R6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="S10" s="13">
+      <c r="S10" s="17">
         <f>S6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
@@ -3201,75 +3791,75 @@
           <t>Survey services revenue</t>
         </is>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="17">
         <f>B7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="17">
         <f>C7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="17">
         <f>D7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="17">
         <f>E7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="17">
         <f>F7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="17">
         <f>G7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="17">
         <f>H7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="17">
         <f>I7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="17">
         <f>J7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="17">
         <f>K7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="L11" s="13">
+      <c r="L11" s="17">
         <f>L7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="17">
         <f>M7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="N11" s="13">
+      <c r="N11" s="17">
         <f>N7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="O11" s="13">
+      <c r="O11" s="17">
         <f>O7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="P11" s="13">
+      <c r="P11" s="17">
         <f>P7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="Q11" s="13">
+      <c r="Q11" s="17">
         <f>Q7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="R11" s="13">
+      <c r="R11" s="17">
         <f>R7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="S11" s="13">
+      <c r="S11" s="17">
         <f>S7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
@@ -3280,75 +3870,75 @@
           <t>TOTAL REVENUE</t>
         </is>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="25">
         <f>B10+B11</f>
         <v/>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="25">
         <f>C10+C11</f>
         <v/>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="25">
         <f>D10+D11</f>
         <v/>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="25">
         <f>E10+E11</f>
         <v/>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="25">
         <f>F10+F11</f>
         <v/>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="25">
         <f>G10+G11</f>
         <v/>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="25">
         <f>H10+H11</f>
         <v/>
       </c>
-      <c r="I12" s="21">
+      <c r="I12" s="25">
         <f>I10+I11</f>
         <v/>
       </c>
-      <c r="J12" s="21">
+      <c r="J12" s="25">
         <f>J10+J11</f>
         <v/>
       </c>
-      <c r="K12" s="21">
+      <c r="K12" s="25">
         <f>K10+K11</f>
         <v/>
       </c>
-      <c r="L12" s="21">
+      <c r="L12" s="25">
         <f>L10+L11</f>
         <v/>
       </c>
-      <c r="M12" s="21">
+      <c r="M12" s="25">
         <f>M10+M11</f>
         <v/>
       </c>
-      <c r="N12" s="21">
+      <c r="N12" s="25">
         <f>N10+N11</f>
         <v/>
       </c>
-      <c r="O12" s="21">
+      <c r="O12" s="25">
         <f>O10+O11</f>
         <v/>
       </c>
-      <c r="P12" s="21">
+      <c r="P12" s="25">
         <f>P10+P11</f>
         <v/>
       </c>
-      <c r="Q12" s="21">
+      <c r="Q12" s="25">
         <f>Q10+Q11</f>
         <v/>
       </c>
-      <c r="R12" s="21">
+      <c r="R12" s="25">
         <f>R10+R11</f>
         <v/>
       </c>
-      <c r="S12" s="21">
+      <c r="S12" s="25">
         <f>S10+S11</f>
         <v/>
       </c>
@@ -3366,75 +3956,75 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="17">
         <f>B10*'Unit Economics'!$B$7+B11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="17">
         <f>C10*'Unit Economics'!$B$7+C11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="17">
         <f>D10*'Unit Economics'!$B$7+D11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="17">
         <f>E10*'Unit Economics'!$B$7+E11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="17">
         <f>F10*'Unit Economics'!$B$7+F11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="17">
         <f>G10*'Unit Economics'!$B$7+G11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="17">
         <f>H10*'Unit Economics'!$B$7+H11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="17">
         <f>I10*'Unit Economics'!$B$7+I11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="17">
         <f>J10*'Unit Economics'!$B$7+J11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="K15" s="13">
+      <c r="K15" s="17">
         <f>K10*'Unit Economics'!$B$7+K11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="L15" s="13">
+      <c r="L15" s="17">
         <f>L10*'Unit Economics'!$B$7+L11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="M15" s="13">
+      <c r="M15" s="17">
         <f>M10*'Unit Economics'!$B$7+M11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="N15" s="13">
+      <c r="N15" s="17">
         <f>N10*'Unit Economics'!$B$7+N11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="O15" s="13">
+      <c r="O15" s="17">
         <f>O10*'Unit Economics'!$B$7+O11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="P15" s="13">
+      <c r="P15" s="17">
         <f>P10*'Unit Economics'!$B$7+P11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="Q15" s="13">
+      <c r="Q15" s="17">
         <f>Q10*'Unit Economics'!$B$7+Q11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="R15" s="13">
+      <c r="R15" s="17">
         <f>R10*'Unit Economics'!$B$7+R11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="S15" s="13">
+      <c r="S15" s="17">
         <f>S10*'Unit Economics'!$B$7+S11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
@@ -3442,435 +4032,435 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Operating costs [CONFIRM all — placeholders below]</t>
+          <t>Operating costs, US$/month [CONFIRM all — placeholders below, sized against the $600K raise]</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Founder comp (Amgad, Diana, Lucas combined)  [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F18" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="I18" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J18" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K18" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="L18" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="M18" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="N18" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="O18" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="P18" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="Q18" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="R18" s="7" t="n">
-        <v>15000</v>
-      </c>
-      <c r="S18" s="7" t="n">
-        <v>15000</v>
+          <t>Founder comp (Amgad, Diana, Lucas combined), US$  [CONFIRM]</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G18" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K18" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L18" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="N18" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O18" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="P18" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Q18" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="R18" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S18" s="11" t="n">
+        <v>3000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CTO hire (from M2)  [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n">
+          <t>CTO hire (from M2), US$  [CONFIRM]</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="C19" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="D19" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="H19" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="J19" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L19" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="M19" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="N19" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="O19" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P19" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="Q19" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="R19" s="7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="S19" s="7" t="n">
-        <v>12000</v>
+      <c r="C19" s="11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="K19" s="11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="M19" s="11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="N19" s="11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O19" s="11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="P19" s="11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="Q19" s="11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="R19" s="11" t="n">
+        <v>2400</v>
+      </c>
+      <c r="S19" s="11" t="n">
+        <v>2400</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Geospatial/data engineer (from M4)  [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n">
+          <t>Geospatial/data engineer (from M4), US$  [CONFIRM]</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="7" t="n">
+      <c r="D20" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="7" t="n">
-        <v>9000</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>9000</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>9000</v>
-      </c>
-      <c r="H20" s="7" t="n">
-        <v>9000</v>
-      </c>
-      <c r="I20" s="7" t="n">
-        <v>9000</v>
-      </c>
-      <c r="J20" s="7" t="n">
-        <v>9000</v>
-      </c>
-      <c r="K20" s="7" t="n">
-        <v>9000</v>
-      </c>
-      <c r="L20" s="7" t="n">
-        <v>9000</v>
-      </c>
-      <c r="M20" s="7" t="n">
-        <v>9000</v>
-      </c>
-      <c r="N20" s="7" t="n">
-        <v>9000</v>
-      </c>
-      <c r="O20" s="7" t="n">
-        <v>9000</v>
-      </c>
-      <c r="P20" s="7" t="n">
-        <v>9000</v>
-      </c>
-      <c r="Q20" s="7" t="n">
-        <v>9000</v>
-      </c>
-      <c r="R20" s="7" t="n">
-        <v>9000</v>
-      </c>
-      <c r="S20" s="7" t="n">
-        <v>9000</v>
+      <c r="E20" s="11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G20" s="11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H20" s="11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="K20" s="11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L20" s="11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M20" s="11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="N20" s="11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="O20" s="11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="P20" s="11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="Q20" s="11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="R20" s="11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="S20" s="11" t="n">
+        <v>1800</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Sales hire (from M5)  [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="n">
+          <t>Sales hire (from M5), US$  [CONFIRM]</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="7" t="n">
+      <c r="D21" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="7" t="n">
+      <c r="E21" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="H21" s="7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="I21" s="7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J21" s="7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="L21" s="7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="M21" s="7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="N21" s="7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="O21" s="7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="P21" s="7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="Q21" s="7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="R21" s="7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="S21" s="7" t="n">
-        <v>8000</v>
+      <c r="F21" s="11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="H21" s="11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="K21" s="11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="L21" s="11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="M21" s="11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="N21" s="11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="O21" s="11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="P21" s="11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="Q21" s="11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="R21" s="11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="S21" s="11" t="n">
+        <v>1600</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Data/infra (satellite APIs, cloud, MapBiomas-class data)  [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="H22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="L22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="M22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="N22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="O22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="P22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="Q22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="R22" s="7" t="n">
-        <v>3000</v>
-      </c>
-      <c r="S22" s="7" t="n">
-        <v>3000</v>
+          <t>Data/infra (satellite APIs, cloud, MapBiomas-class data), US$  [CONFIRM]</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="K22" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="L22" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="M22" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="N22" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="O22" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="P22" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="Q22" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="R22" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="S22" s="11" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Legal &amp; entity setup (front-loaded M1-M3)  [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E23" s="7" t="n">
+          <t>Legal &amp; entity setup — Delaware + Brazilian LTDA formation (front-loaded M1-M3), US$  [CONFIRM]</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="7" t="n">
+      <c r="G23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="7" t="n">
+      <c r="H23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="7" t="n">
+      <c r="I23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="7" t="n">
+      <c r="J23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="K23" s="7" t="n">
+      <c r="K23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L23" s="7" t="n">
+      <c r="L23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="M23" s="7" t="n">
+      <c r="M23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N23" s="7" t="n">
+      <c r="N23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O23" s="7" t="n">
+      <c r="O23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="P23" s="7" t="n">
+      <c r="P23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" s="7" t="n">
+      <c r="Q23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="R23" s="7" t="n">
+      <c r="R23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="S23" s="7" t="n">
+      <c r="S23" s="11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>G&amp;A / other  [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C24" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H24" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I24" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J24" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="L24" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M24" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="N24" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="O24" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="P24" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="Q24" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="R24" s="7" t="n">
-        <v>4000</v>
-      </c>
-      <c r="S24" s="7" t="n">
-        <v>4000</v>
+          <t>G&amp;A / other, US$  [CONFIRM]</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G24" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="H24" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="J24" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="K24" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="L24" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="M24" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="N24" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="O24" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="P24" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="Q24" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="R24" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="S24" s="11" t="n">
+        <v>800</v>
       </c>
     </row>
     <row r="25">
@@ -3879,75 +4469,75 @@
           <t>TOTAL OPERATING COSTS</t>
         </is>
       </c>
-      <c r="B25" s="21">
+      <c r="B25" s="25">
         <f>SUM(B18:B24)</f>
         <v/>
       </c>
-      <c r="C25" s="21">
+      <c r="C25" s="25">
         <f>SUM(C18:C24)</f>
         <v/>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="25">
         <f>SUM(D18:D24)</f>
         <v/>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="25">
         <f>SUM(E18:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="21">
+      <c r="F25" s="25">
         <f>SUM(F18:F24)</f>
         <v/>
       </c>
-      <c r="G25" s="21">
+      <c r="G25" s="25">
         <f>SUM(G18:G24)</f>
         <v/>
       </c>
-      <c r="H25" s="21">
+      <c r="H25" s="25">
         <f>SUM(H18:H24)</f>
         <v/>
       </c>
-      <c r="I25" s="21">
+      <c r="I25" s="25">
         <f>SUM(I18:I24)</f>
         <v/>
       </c>
-      <c r="J25" s="21">
+      <c r="J25" s="25">
         <f>SUM(J18:J24)</f>
         <v/>
       </c>
-      <c r="K25" s="21">
+      <c r="K25" s="25">
         <f>SUM(K18:K24)</f>
         <v/>
       </c>
-      <c r="L25" s="21">
+      <c r="L25" s="25">
         <f>SUM(L18:L24)</f>
         <v/>
       </c>
-      <c r="M25" s="21">
+      <c r="M25" s="25">
         <f>SUM(M18:M24)</f>
         <v/>
       </c>
-      <c r="N25" s="21">
+      <c r="N25" s="25">
         <f>SUM(N18:N24)</f>
         <v/>
       </c>
-      <c r="O25" s="21">
+      <c r="O25" s="25">
         <f>SUM(O18:O24)</f>
         <v/>
       </c>
-      <c r="P25" s="21">
+      <c r="P25" s="25">
         <f>SUM(P18:P24)</f>
         <v/>
       </c>
-      <c r="Q25" s="21">
+      <c r="Q25" s="25">
         <f>SUM(Q18:Q24)</f>
         <v/>
       </c>
-      <c r="R25" s="21">
+      <c r="R25" s="25">
         <f>SUM(R18:R24)</f>
         <v/>
       </c>
-      <c r="S25" s="21">
+      <c r="S25" s="25">
         <f>SUM(S18:S24)</f>
         <v/>
       </c>
@@ -3965,75 +4555,75 @@
           <t>Net burn (gross profit − opex)</t>
         </is>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="17">
         <f>B15-B25</f>
         <v/>
       </c>
-      <c r="C28" s="13">
+      <c r="C28" s="17">
         <f>C15-C25</f>
         <v/>
       </c>
-      <c r="D28" s="13">
+      <c r="D28" s="17">
         <f>D15-D25</f>
         <v/>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="17">
         <f>E15-E25</f>
         <v/>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="17">
         <f>F15-F25</f>
         <v/>
       </c>
-      <c r="G28" s="13">
+      <c r="G28" s="17">
         <f>G15-G25</f>
         <v/>
       </c>
-      <c r="H28" s="13">
+      <c r="H28" s="17">
         <f>H15-H25</f>
         <v/>
       </c>
-      <c r="I28" s="13">
+      <c r="I28" s="17">
         <f>I15-I25</f>
         <v/>
       </c>
-      <c r="J28" s="13">
+      <c r="J28" s="17">
         <f>J15-J25</f>
         <v/>
       </c>
-      <c r="K28" s="13">
+      <c r="K28" s="17">
         <f>K15-K25</f>
         <v/>
       </c>
-      <c r="L28" s="13">
+      <c r="L28" s="17">
         <f>L15-L25</f>
         <v/>
       </c>
-      <c r="M28" s="13">
+      <c r="M28" s="17">
         <f>M15-M25</f>
         <v/>
       </c>
-      <c r="N28" s="13">
+      <c r="N28" s="17">
         <f>N15-N25</f>
         <v/>
       </c>
-      <c r="O28" s="13">
+      <c r="O28" s="17">
         <f>O15-O25</f>
         <v/>
       </c>
-      <c r="P28" s="13">
+      <c r="P28" s="17">
         <f>P15-P25</f>
         <v/>
       </c>
-      <c r="Q28" s="13">
+      <c r="Q28" s="17">
         <f>Q15-Q25</f>
         <v/>
       </c>
-      <c r="R28" s="13">
+      <c r="R28" s="17">
         <f>R15-R25</f>
         <v/>
       </c>
-      <c r="S28" s="13">
+      <c r="S28" s="17">
         <f>S15-S25</f>
         <v/>
       </c>
@@ -4041,78 +4631,78 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Cash balance (starting: R$3,000,000 raise)</t>
-        </is>
-      </c>
-      <c r="B29" s="13">
-        <f>3000000+B28</f>
-        <v/>
-      </c>
-      <c r="C29" s="13">
+          <t>Cash balance, US$ (starting: US$600,000 raise)</t>
+        </is>
+      </c>
+      <c r="B29" s="17">
+        <f>600000+B28</f>
+        <v/>
+      </c>
+      <c r="C29" s="17">
         <f>B29+C28</f>
         <v/>
       </c>
-      <c r="D29" s="13">
+      <c r="D29" s="17">
         <f>C29+D28</f>
         <v/>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="17">
         <f>D29+E28</f>
         <v/>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="17">
         <f>E29+F28</f>
         <v/>
       </c>
-      <c r="G29" s="13">
+      <c r="G29" s="17">
         <f>F29+G28</f>
         <v/>
       </c>
-      <c r="H29" s="13">
+      <c r="H29" s="17">
         <f>G29+H28</f>
         <v/>
       </c>
-      <c r="I29" s="13">
+      <c r="I29" s="17">
         <f>H29+I28</f>
         <v/>
       </c>
-      <c r="J29" s="13">
+      <c r="J29" s="17">
         <f>I29+J28</f>
         <v/>
       </c>
-      <c r="K29" s="13">
+      <c r="K29" s="17">
         <f>J29+K28</f>
         <v/>
       </c>
-      <c r="L29" s="13">
+      <c r="L29" s="17">
         <f>K29+L28</f>
         <v/>
       </c>
-      <c r="M29" s="13">
+      <c r="M29" s="17">
         <f>L29+M28</f>
         <v/>
       </c>
-      <c r="N29" s="13">
+      <c r="N29" s="17">
         <f>M29+N28</f>
         <v/>
       </c>
-      <c r="O29" s="13">
+      <c r="O29" s="17">
         <f>N29+O28</f>
         <v/>
       </c>
-      <c r="P29" s="13">
+      <c r="P29" s="17">
         <f>O29+P28</f>
         <v/>
       </c>
-      <c r="Q29" s="13">
+      <c r="Q29" s="17">
         <f>P29+Q28</f>
         <v/>
       </c>
-      <c r="R29" s="13">
+      <c r="R29" s="17">
         <f>Q29+R28</f>
         <v/>
       </c>
-      <c r="S29" s="13">
+      <c r="S29" s="17">
         <f>R29+S28</f>
         <v/>
       </c>
@@ -4210,7 +4800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4229,14 +4819,14 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Scenarios — Bull / Base / Bear</t>
+          <t>Scenarios (Bottom-Up) — Bull / Base / Bear</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Applies multipliers to the Base case's two growth drivers (hectare growth, survey volume) from the Budget tab, per the ranges set out in Hypotheses. This is a summary/comparison view, not a separately-modeled set of tabs — the Budget tab remains the single source of the base case's month-by-month detail.</t>
+          <t>SUPPORTING sensitivity view on the bottom-up 'Budget (Base)' build — not the official forecast (see 'Scenarios (Deck)' for that). Applies multipliers to the Base case's two growth drivers (hectare growth, survey volume) from the Budget tab, per the ranges set out in Hypotheses. Figures in US$. This is a summary/comparison view, not a separately-modeled set of tabs — the Budget tab remains the single source of the base case's month-by-month detail.</t>
         </is>
       </c>
     </row>
@@ -4275,10 +4865,10 @@
           <t>Bear</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="24" t="n">
         <v>0.7</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -4293,10 +4883,10 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="24" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -4311,10 +4901,10 @@
           <t>Bull</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="24" t="n">
         <v>1.75</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="24" t="n">
         <v>1.4</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -4343,12 +4933,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Total 18mo revenue (R$)</t>
+          <t>Total 18mo revenue (US$)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Cash balance at M18 (R$)</t>
+          <t>Cash balance at M18 (US$)</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -4363,16 +4953,16 @@
           <t>Bear</t>
         </is>
       </c>
-      <c r="B13" s="22">
+      <c r="B13" s="26">
         <f>ROUND('Budget (Base)'!S6*B7,0)</f>
         <v/>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="17">
         <f>SUM('Budget (Base)'!B12:S12)*((B7+C7)/2)</f>
         <v/>
       </c>
-      <c r="D13" s="13">
-        <f>3000000+C13-(AVERAGE('Budget (Base)'!B25:S25)*18)</f>
+      <c r="D13" s="17">
+        <f>600000+C13-(AVERAGE('Budget (Base)'!B25:S25)*18)</f>
         <v/>
       </c>
       <c r="E13" t="inlineStr">
@@ -4387,15 +4977,15 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="26">
         <f>'Budget (Base)'!S6</f>
         <v/>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="17">
         <f>SUM('Budget (Base)'!B12:S12)</f>
         <v/>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="17">
         <f>'Budget (Base)'!S29</f>
         <v/>
       </c>
@@ -4411,16 +5001,16 @@
           <t>Bull</t>
         </is>
       </c>
-      <c r="B15" s="22">
+      <c r="B15" s="26">
         <f>ROUND('Budget (Base)'!S6*B9,0)</f>
         <v/>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="17">
         <f>SUM('Budget (Base)'!B12:S12)*((B9+C9)/2)</f>
         <v/>
       </c>
-      <c r="D15" s="13">
-        <f>3000000+C15-(AVERAGE('Budget (Base)'!B25:S25)*18)</f>
+      <c r="D15" s="17">
+        <f>600000+C15-(AVERAGE('Budget (Base)'!B25:S25)*18)</f>
         <v/>
       </c>
       <c r="E15" t="inlineStr">
@@ -4447,7 +5037,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4471,35 +5061,35 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Mirrors 04-investment-documents/CAP_TABLE.md. Founder split and pool size below are illustrative placeholders — edit green cells.</t>
+          <t>Mirrors 04-investment-documents/CAP_TABLE.md. Raise/cap/% are confirmed by the pitch deck's ask slide. Founder split and pool size below remain illustrative placeholders — edit green cells.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SAFE mechanics (fixed by term sheet)</t>
+          <t>SAFE mechanics (confirmed by pitch deck's ask slide)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Raise (R$)</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>3000000</v>
+          <t>Raise (US$)</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>600000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Post-money valuation cap (R$)</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>20000000</v>
+          <t>Post-money valuation cap (US$)</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>4000000</v>
       </c>
     </row>
     <row r="8">
@@ -4508,7 +5098,7 @@
           <t>SAFE holders' post-money %</t>
         </is>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="9">
         <f>B6/B7</f>
         <v/>
       </c>
@@ -4519,7 +5109,7 @@
           <t>Option pool %  [CONFIRM]</t>
         </is>
       </c>
-      <c r="B9" s="24" t="n">
+      <c r="B9" s="27" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4529,7 +5119,7 @@
           <t>Remaining for founders %</t>
         </is>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="9">
         <f>1-B8-B9</f>
         <v/>
       </c>
@@ -4564,10 +5154,10 @@
           <t>Amgad</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n">
+      <c r="B14" s="27" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="9">
         <f>B14*$B$10</f>
         <v/>
       </c>
@@ -4578,10 +5168,10 @@
           <t>Diana Dutra</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n">
+      <c r="B15" s="27" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="9">
         <f>B15*$B$10</f>
         <v/>
       </c>
@@ -4592,10 +5182,10 @@
           <t>Lucas Costa</t>
         </is>
       </c>
-      <c r="B16" s="24" t="n">
+      <c r="B16" s="27" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="9">
         <f>B16*$B$10</f>
         <v/>
       </c>
@@ -4606,7 +5196,7 @@
           <t>SAFE holders (class)</t>
         </is>
       </c>
-      <c r="C17" s="23">
+      <c r="C17" s="9">
         <f>B8</f>
         <v/>
       </c>
@@ -4617,19 +5207,19 @@
           <t>Option pool</t>
         </is>
       </c>
-      <c r="C18" s="23">
+      <c r="C18" s="9">
         <f>B9</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="25">
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="28">
         <f>SUM(C14:C18)</f>
         <v/>
       </c>
@@ -4641,153 +5231,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Use of Funds</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Mirrors 04-investment-documents/USE_OF_FUNDS.md. Edit % column — R$ and totals recompute.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Total raise (R$)</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="n">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>% of raise  [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>R$</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Engineering / product (CTO + geospatial engineer)</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="C8" s="13">
-        <f>B8*$B$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sales &amp; commercial</t>
-        </is>
-      </c>
-      <c r="B9" s="24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C9" s="13">
-        <f>B9*$B$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Operations (survey delivery capacity)</t>
-        </is>
-      </c>
-      <c r="B10" s="24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C10" s="13">
-        <f>B10*$B$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Legal &amp; entity structure</t>
-        </is>
-      </c>
-      <c r="B11" s="24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C11" s="13">
-        <f>B11*$B$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Working capital / runway buffer</t>
-        </is>
-      </c>
-      <c r="B12" s="24" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C12" s="13">
-        <f>B12*$B$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B13" s="25">
-        <f>SUM(B8:B12)</f>
-        <v/>
-      </c>
-      <c r="C13" s="21">
-        <f>SUM(C8:C12)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A3:C3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data-room/07-financials/FINANCIAL_MODEL.xlsx
+++ b/data-room/07-financials/FINANCIAL_MODEL.xlsx
@@ -1,36 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="5" activeTab="9" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Hypotheses" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Scenarios (Deck)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Unit Economics" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Pipeline" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Actuals" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Budget (Base)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Scenarios (Bottom-Up)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Cap Table" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Use of Funds" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hypotheses" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios (Deck)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Economics" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget (Base)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios (Bottom-Up)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cap Table" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Use of Funds" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="#,##0;[RED]-#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0;[Red]\-#,##0"/>
+    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00&quot; US$M&quot;"/>
+    <numFmt numFmtId="168" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,12 +41,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00F2EFE6"/>
+      <color rgb="FFF2EFE6"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF1C2A20"/>
+      <sz val="11"/>
     </font>
     <font>
       <i val="1"/>
@@ -53,10 +70,13 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001C2A20"/>
+      <color rgb="00842029"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -65,12 +85,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001C2A20"/>
+        <fgColor rgb="FF1C2A20"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5A72C"/>
+        <fgColor rgb="FFE5A72C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF3EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -78,17 +108,21 @@
         <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAF3EA"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -99,11 +133,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -112,38 +143,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -218,48 +282,132 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1600" b="0" i="0" strike="noStrike" kern="1200" spc="50" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mj-lt"/>
+                <a:ea typeface="+mj-ea"/>
+                <a:cs typeface="+mj-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
+              <a:rPr lang="pt-BR"/>
               <a:t>Revenue projected in three scenarios (US$M/year) — from the pitch deck</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="1"/>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+      <txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="1600" b="0" i="0" strike="noStrike" kern="1200" spc="50" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mj-lt"/>
+              <a:ea typeface="+mj-ea"/>
+              <a:cs typeface="+mj-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t>None</a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </txPr>
     </title>
     <plotArea>
+      <layout/>
       <barChart>
         <barDir val="col"/>
         <grouping val="clustered"/>
+        <varyColors val="1"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Scenarios (Deck)'!B7</f>
+              <f>'Scenarios (Deck)'!$B$7</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Pessimista (US$M)</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:schemeClr val="accent1">
+                <a:alpha val="70000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="1"/>
           <cat>
             <numRef>
               <f>'Scenarios (Deck)'!$A$8:$A$10</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>2027</v>
+                </pt>
+                <pt idx="1">
+                  <v>2028</v>
+                </pt>
+                <pt idx="2">
+                  <v>2029</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Scenarios (Deck)'!$B$8:$B$10</f>
+              <numCache>
+                <formatCode>#,##0.00</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>0.18</v>
+                </pt>
+                <pt idx="1">
+                  <v>0.66</v>
+                </pt>
+                <pt idx="2">
+                  <v>1.6</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -268,22 +416,61 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Scenarios (Deck)'!C7</f>
+              <f>'Scenarios (Deck)'!$C$7</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Base (US$M)</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:schemeClr val="accent2">
+                <a:alpha val="70000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="1"/>
           <cat>
             <numRef>
               <f>'Scenarios (Deck)'!$A$8:$A$10</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>2027</v>
+                </pt>
+                <pt idx="1">
+                  <v>2028</v>
+                </pt>
+                <pt idx="2">
+                  <v>2029</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Scenarios (Deck)'!$C$8:$C$10</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>0.38</v>
+                </pt>
+                <pt idx="1">
+                  <v>1.32</v>
+                </pt>
+                <pt idx="2">
+                  <v>3.5</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
@@ -292,26 +479,74 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Scenarios (Deck)'!D7</f>
+              <f>'Scenarios (Deck)'!$D$7</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Otimista (US$M)</v>
+                </pt>
+              </strCache>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:schemeClr val="accent3">
+                <a:alpha val="70000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="1"/>
           <cat>
             <numRef>
               <f>'Scenarios (Deck)'!$A$8:$A$10</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>2027</v>
+                </pt>
+                <pt idx="1">
+                  <v>2028</v>
+                </pt>
+                <pt idx="2">
+                  <v>2029</v>
+                </pt>
+              </numCache>
             </numRef>
           </cat>
           <val>
             <numRef>
               <f>'Scenarios (Deck)'!$D$8:$D$10</f>
+              <numCache>
+                <formatCode>#,##0.00</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>0.58</v>
+                </pt>
+                <pt idx="1">
+                  <v>2</v>
+                </pt>
+                <pt idx="2">
+                  <v>4.56</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <gapWidth val="80"/>
+        <overlap val="25"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -320,84 +555,362 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="pt-BR"/>
                   <a:t>Year</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <overlay val="1"/>
+          <spPr>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t>None</a:t>
+              </a:r>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </txPr>
         </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="15875" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" spc="20" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>None</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="pt-BR"/>
                   <a:t>US$ millions/year</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <layout>
+            <manualLayout>
+              <xMode val="edge"/>
+              <yMode val="edge"/>
+              <wMode val="factor"/>
+              <hMode val="factor"/>
+              <x val="0.04650252525252525"/>
+              <y val="0.3145696969696969"/>
+            </manualLayout>
+          </layout>
+          <overlay val="1"/>
+          <spPr>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t>None</a:t>
+              </a:r>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </txPr>
         </title>
+        <numFmt formatCode="#,##0.00" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>None</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+      <txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t>None</a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </txPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+      <a:round/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
+              <a:rPr lang="pt-BR"/>
               <a:t>Bottom-up build — Revenue vs. Cash balance (US$)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <overlay val="1"/>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+      <txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t>None</a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </txPr>
     </title>
     <plotArea>
+      <layout/>
       <lineChart>
         <grouping val="standard"/>
+        <varyColors val="1"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
@@ -405,28 +918,97 @@
             <v>Total revenue</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$B$12</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>6033.333333333333</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="1"/>
@@ -435,947 +1017,3443 @@
             <v>Cash balance</v>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$C$12</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>6070</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="2"/>
           <order val="2"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$D$12</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>6110.333333333333</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="3"/>
           <order val="3"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$E$12</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>9154.700000000001</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="4"/>
           <order val="4"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$F$12</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>9203.503333333334</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="5"/>
           <order val="5"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$G$12</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>9257.187</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="6"/>
           <order val="6"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$H$12</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>9316.239033333333</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="7"/>
           <order val="7"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$I$12</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>12381.19627</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="8"/>
           <order val="8"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$J$12</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>12452.64923033333</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="9"/>
           <order val="9"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$K$12</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>12531.2474867</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="10"/>
           <order val="10"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$L$12</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>12617.70556870333</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="11"/>
           <order val="11"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$M$12</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>15712.809458907</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="12"/>
           <order val="12"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$N$12</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>15817.42373813103</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="13"/>
           <order val="13"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$O$12</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>15932.49944527747</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="14"/>
           <order val="14"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$P$12</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>16059.08272313855</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="15"/>
           <order val="15"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$Q$12</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>19198.32432878574</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="16"/>
           <order val="16"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$R$12</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>19351.49009499765</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="17"/>
           <order val="17"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$S$12</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>19519.97243783074</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="18"/>
           <order val="18"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$B$29</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>597923.3333333334</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="19"/>
           <order val="19"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$C$29</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>593472.3333333334</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="20"/>
           <order val="20"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$D$29</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>589049.5666666667</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="21"/>
           <order val="21"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$E$29</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>585507.8566666667</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="22"/>
           <order val="22"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$F$29</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>580400.309</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="23"/>
           <order val="23"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$G$29</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>575330.3399</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="24"/>
           <order val="24"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$H$29</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>570301.7072233333</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="25"/>
           <order val="25"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$I$29</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>566968.5446123333</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="26"/>
           <order val="26"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$J$29</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>563685.3990735667</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="27"/>
           <order val="27"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$K$29</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>560457.2723142566</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="28"/>
           <order val="28"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$L$29</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>557289.666212349</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="29"/>
           <order val="29"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$M$29</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>555838.6328335839</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="30"/>
           <order val="30"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$N$29</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>554460.8294502756</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="31"/>
           <order val="31"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$O$29</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>553163.5790619699</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="32"/>
           <order val="32"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$P$29</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>551954.9369681668</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="33"/>
           <order val="33"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$Q$29</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>552493.7639983168</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="34"/>
           <order val="34"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$R$29</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>553139.8070648152</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <ser>
           <idx val="35"/>
           <order val="35"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:prstDash val="solid"/>
+              <a:round/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Budget (Base)'!$B$5:$S$5</f>
-            </numRef>
+              <strCache>
+                <ptCount val="18"/>
+                <pt idx="0">
+                  <v>M1</v>
+                </pt>
+                <pt idx="1">
+                  <v>M2</v>
+                </pt>
+                <pt idx="2">
+                  <v>M3</v>
+                </pt>
+                <pt idx="3">
+                  <v>M4</v>
+                </pt>
+                <pt idx="4">
+                  <v>M5</v>
+                </pt>
+                <pt idx="5">
+                  <v>M6</v>
+                </pt>
+                <pt idx="6">
+                  <v>M7</v>
+                </pt>
+                <pt idx="7">
+                  <v>M8</v>
+                </pt>
+                <pt idx="8">
+                  <v>M9</v>
+                </pt>
+                <pt idx="9">
+                  <v>M10</v>
+                </pt>
+                <pt idx="10">
+                  <v>M11</v>
+                </pt>
+                <pt idx="11">
+                  <v>M12</v>
+                </pt>
+                <pt idx="12">
+                  <v>M13</v>
+                </pt>
+                <pt idx="13">
+                  <v>M14</v>
+                </pt>
+                <pt idx="14">
+                  <v>M15</v>
+                </pt>
+                <pt idx="15">
+                  <v>M16</v>
+                </pt>
+                <pt idx="16">
+                  <v>M17</v>
+                </pt>
+                <pt idx="17">
+                  <v>M18</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Budget (Base)'!$S$29</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>553903.7877712967</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <smooth val="0"/>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -1384,105 +4462,466 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="pt-BR"/>
                   <a:t>Month</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <overlay val="1"/>
+          <spPr>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t>None</a:t>
+              </a:r>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </txPr>
         </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>None</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="pt-BR"/>
                   <a:t>US$</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <overlay val="1"/>
+          <spPr>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t>None</a:t>
+              </a:r>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </txPr>
         </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>None</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+      <txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t>None</a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </txPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+      <a:round/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1600" b="0" i="0" strike="noStrike" kern="1200" spc="50" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mj-lt"/>
+                <a:ea typeface="+mj-ea"/>
+                <a:cs typeface="+mj-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>18-month total revenue by scenario (bottom-up build, US$)</a:t>
+              <a:rPr lang="pt-BR"/>
+              <a:t>18-month total revenue by scenario (bottom-up build   US$)</a:t>
             </a:r>
           </a:p>
         </rich>
       </tx>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1054327160493827"/>
+          <y val="0.01959876543209877"/>
+        </manualLayout>
+      </layout>
+      <overlay val="1"/>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+      <txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="1600" b="0" i="0" strike="noStrike" kern="1200" spc="50" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mj-lt"/>
+              <a:ea typeface="+mj-ea"/>
+              <a:cs typeface="+mj-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t>None</a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </txPr>
     </title>
     <plotArea>
+      <layout/>
       <barChart>
         <barDir val="col"/>
         <grouping val="clustered"/>
+        <varyColors val="1"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="1"/>
+          <dPt>
+            <idx val="0"/>
+            <invertIfNegative val="1"/>
+            <bubble3D val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:schemeClr val="accent1">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <invertIfNegative val="1"/>
+            <bubble3D val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:schemeClr val="accent2">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <invertIfNegative val="1"/>
+            <bubble3D val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:schemeClr val="accent3">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Scenarios (Bottom-Up)'!$A$13:$A$15</f>
-            </numRef>
+              <strCache>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>Bear</v>
+                </pt>
+                <pt idx="1">
+                  <v>Base</v>
+                </pt>
+                <pt idx="2">
+                  <v>Bull</v>
+                </pt>
+              </strCache>
+            </strRef>
           </cat>
           <val>
             <numRef>
               <f>'Scenarios (Bottom-Up)'!$C$13:$C$15</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="3"/>
+                <pt idx="0">
+                  <v>136031.8180896829</v>
+                </pt>
+                <pt idx="1">
+                  <v>226719.6968161382</v>
+                </pt>
+                <pt idx="2">
+                  <v>357083.5224854176</v>
+                </pt>
+              </numCache>
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <gapWidth val="80"/>
+        <overlap val="25"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -1491,50 +4930,335 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="15875" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" spc="20" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>None</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
         <lblOffset val="100"/>
+        <noMultiLvlLbl val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
+                  <a:rPr lang="pt-BR"/>
                   <a:t>US$</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <layout>
+            <manualLayout>
+              <xMode val="edge"/>
+              <yMode val="edge"/>
+              <wMode val="factor"/>
+              <hMode val="factor"/>
+              <x val="0.02155864197530864"/>
+              <y val="0.4092086419753087"/>
+            </manualLayout>
+          </layout>
+          <overlay val="1"/>
+          <spPr>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:r>
+                <a:t>None</a:t>
+              </a:r>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </txPr>
         </title>
+        <numFmt formatCode="General" sourceLinked="1"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>None</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </txPr>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+      <txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t>None</a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </txPr>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+      <a:round/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Claude — data-room fix</author>
+  </authors>
+  <commentList>
+    <comment ref="C9" authorId="0" shapeId="0">
+      <text>
+        <t>This holds a bare number (50000) where every other row in this column holds a description (e.g. "20% converts by M12"). It also doesn't match Pipeline!C6 (5,000,000 ha) or Pipeline!E6 (5% probability) for the same Coplacana account — worth reconciling which figures are current, and rewriting this cell as a description consistent with the rest of the column.</t>
+      </text>
+    </comment>
+    <comment ref="E11" authorId="0" shapeId="0">
+      <text>
+        <t>Bear-case gross margin (70%) is now identical to the Base case (70%, cell C11) — a bear scenario should model something worse than base, not the same number. Base margin was lowered from 80% to 70% without lowering Bear correspondingly (still at its original 70%, which used to be below an 80% base).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Claude — data-room fix</author>
+  </authors>
+  <commentList>
+    <comment ref="B24" authorId="0" shapeId="0">
+      <text>
+        <t>LTV ($3,500, from B14) is lower than CAC ($6,000, from B22) — the model currently implies AgrosTech loses ~$2,500 acquiring each subscription customer. Before this goes in front of an investor, either B22's CAC needs a real source (it reads as a placeholder guess, not a measured figure — there's no paid-acquisition history yet per B22's original note), or B9 (avg. hectares/customer) and B12 (churn) need to reflect the actual target customer profile. A $6,000 CAC implies an enterprise/institutional sales motion (banks, cooperatives) rather than a 1,500ha average account — if that's the intent, this ratio should be computed against a larger avg.-hectares assumption, not the current B9.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Claude — data-room fix</author>
+  </authors>
+  <commentList>
+    <comment ref="C6" authorId="0" shapeId="0">
+      <text>
+        <t>5,000,000 ha for a single cooperative account is larger than most of Brazil's entire soy-planted area (~45M ha nationally, per 06-customers/MARKET_RESEARCH.md). This almost certainly has extra zeros — worth checking whether this was meant to be 5,000 ha before this pipeline table is shown to anyone.</t>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0" shapeId="0">
+      <text>
+        <t>500,000 ha for this contact also looks like it may have extra zeros — worth double-checking the intended scale.</t>
+      </text>
+    </comment>
+    <comment ref="B9" authorId="0" shapeId="0">
+      <text>
+        <t>"Bradesco, itau" are banks, not landholders — putting them in a row with a Hectares figure (100,000) conflates two different things: a bank's own land (none) vs. the land area of the rural-credit portfolio they'd want monitored. If these are real institutional prospects, they probably deserve their own row(s) with a clearly-labeled metric (e.g. "hectares in their credit portfolio"), separate from the consultant/producer rows above.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Claude — data-room fix</author>
+  </authors>
+  <commentList>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>A6 (Fabio's row) is a real Excel date, now formatted DD/MM/YYYY. This cell is stored as plain text instead, so it won't sort, filter, or compute date-math correctly. Worth converting to a real date value in the same format for consistency.</t>
+      </text>
+    </comment>
+    <comment ref="B13" authorId="0" shapeId="0">
+      <text>
+        <t>This was a hardcoded 10, disconnected from the cash ($200) and burn ($5/mo) cells above it — 200/5 actually equals 40 months, not 10. Converted to a live formula (=B11/B12) so it can't drift out of sync again. Separately: $200 cash and $5/mo burn are very small in absolute terms for a company that just closed a $600K raise — worth double-checking these aren't missing a thousands multiplier (e.g. $200K / $5K).</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Claude — data-room fix</author>
+  </authors>
+  <commentList>
+    <comment ref="A18" authorId="0" shapeId="0">
+      <text>
+        <t>As entered, Amgad (70%) + Diana (10%) + Lucas (8%) = 88% of the founder pool, not 100%. This row makes the 12% gap visible and keeps the TOTAL below correct, instead of letting it silently disappear. Replace this row once you confirm with the founder what the missing 12% is: a rounding fix to the three splits above (e.g. 70/17/13, 74/13/13, etc.), a reserved slot for a future co-founder/early hire, or something else.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -1549,9 +5273,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1561,7 +5285,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -1576,9 +5300,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1588,13 +5312,13 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>0</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
+      <colOff>395111</colOff>
+      <row>17</row>
+      <rowOff>159925</rowOff>
     </from>
     <ext cx="6480000" cy="3240000"/>
     <graphicFrame>
@@ -1603,9 +5327,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1904,76 +5628,70 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="100" customWidth="1" style="24" min="1" max="1"/>
+    <col width="12" customWidth="1" style="24" min="2" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22.05" customHeight="1" s="24">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>AgrosTech — Financial Model v2.0</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>How to use this workbook</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>• Yellow cells = [CONFIRM]: placeholder assumptions the founder needs to validate before this leaves internal use.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>• Green cells = assumption inputs that drive formulas elsewhere — change these, not the formula cells, to update the model.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>• v2.0: reconciled against the founder's pitch deck (AgrosTech_Pitch_Narrativo.pdf, 2026-09-24). USD is now the primary currency throughout (the SAFE is a US-dollar instrument) — R$ shown as a secondary reference at an assumed ~R$5.00/US$1.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>• Core confirmed numbers: US$0.80/ha/year subscription (Passaporte de Crédito Rural) + one-off survey services; US$600,000 raise at a US$4,000,000 post-money cap (15%), 4yr vesting/1yr cliff.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>• It intentionally does NOT use the older R$35-120/ha drone-mission pricing in knowledge-base/PRICING_MODEL.md — that belonged to a prior services-only version of the business model.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>• Tabs: Hypotheses -&gt; 'Scenarios (Deck)' [the OFFICIAL forecast, taken directly from the pitch deck] -&gt; Unit Economics -&gt; Pipeline -&gt; Actuals -&gt; Budget (18mo) [a supporting bottom-up build, see its own note] -&gt; Scenarios (Bottom-Up) -&gt; Cap Table -&gt; Use of Funds.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>• 'Scenarios (Deck)' is the number to lead with in investor conversations — it's the founder's own stated forecast. The 'Budget (Base)' / 'Scenarios (Bottom-Up)' tabs are an independent monthly build from named pipeline + cost assumptions, useful as a sanity check and for burn/runway planning, but on a different time basis (rolling 18mo from raise-close vs. calendar year) — the two are not expected to match exactly, and that's noted on both tabs.</t>
         </is>
@@ -1981,9 +5699,9 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A4:H4"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A9:H9"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A5:H5"/>
@@ -2001,26 +5719,22 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="64.44140625" bestFit="1" customWidth="1" style="24" min="1" max="1"/>
+    <col width="20" customWidth="1" style="24" min="2" max="2"/>
+    <col width="18" customWidth="1" style="24" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22.05" customHeight="1" s="24">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Use of Funds</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Mirrors 04-investment-documents/USE_OF_FUNDS.md. Percentages confirmed directly on the pitch deck's 'O Pedido' slide — goal: get 1.5 million hectares 'in sight' by 2028.</t>
-        </is>
-      </c>
+      <c r="A3" s="21" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2028,22 +5742,22 @@
           <t>Total raise (US$)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="8" t="n">
         <v>600000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>% of raise (confirmed — deck)</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">% of raise </t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>US$</t>
         </is>
@@ -2052,13 +5766,13 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dados e IA (Data &amp; AI — the M1/M2/M3 model stack)</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="n">
+          <t>Dados e IA (Data, platform, hardware &amp; AI — the M1/M2/M3 model stack)</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
         <v>0.4</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="8">
         <f>B8*$B$5</f>
         <v/>
       </c>
@@ -2069,10 +5783,10 @@
           <t>Vendas institucionais (Institutional sales — banks, cooperatives, credit desks)</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n">
+      <c r="B9" s="17" t="n">
         <v>0.3</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="8">
         <f>B9*$B$5</f>
         <v/>
       </c>
@@ -2083,10 +5797,10 @@
           <t>Operações e reserva (Operations &amp; reserve)</t>
         </is>
       </c>
-      <c r="B10" s="27" t="n">
+      <c r="B10" s="17" t="n">
         <v>0.2</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="8">
         <f>B10*$B$5</f>
         <v/>
       </c>
@@ -2097,25 +5811,25 @@
           <t>Integrações Bacen e segurança (Bacen integrations &amp; security)</t>
         </is>
       </c>
-      <c r="B11" s="27" t="n">
+      <c r="B11" s="17" t="n">
         <v>0.1</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="8">
         <f>B11*$B$5</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="18">
         <f>SUM(B8:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="15">
         <f>SUM(C8:C11)</f>
         <v/>
       </c>
@@ -2136,448 +5850,442 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" style="24" min="1" max="1"/>
+    <col width="30" customWidth="1" style="24" min="2" max="2"/>
+    <col width="29.88671875" customWidth="1" style="27" min="3" max="3"/>
+    <col width="22" customWidth="1" style="24" min="4" max="4"/>
+    <col width="21.109375" customWidth="1" style="24" min="5" max="5"/>
+    <col width="22.5546875" customWidth="1" style="24" min="6" max="6"/>
+    <col width="33.77734375" bestFit="1" customWidth="1" style="24" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22.05" customHeight="1" s="24">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Hypotheses Behind the Model</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="30" customHeight="1" s="24">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>Per the checklist: "the assumptions behind each scenario, written out so they can be challenged." Every number in Budget/Scenarios traces back to one of these rows.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Hypothesis</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Base case value</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>Bull case</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>Bear case</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="n">
+    <row r="6" ht="28.8" customHeight="1" s="24">
+      <c r="A6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Subscription price</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>US$ 0.80/ha/year (≈R$4.00)</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>US$ 0.80/ha/year (unchanged)</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>US$ 0.64/ha/year (-20%, price pressure)</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Confirmed by founder and by the deck's 'O Mercado' slide</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
+    <row r="7" ht="43.2" customHeight="1" s="24">
+      <c r="A7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Avg. one-off survey fee</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>R$ 15,000/survey [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>R$ 18,000/survey</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>R$ 15,000</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>R$ 20,000/survey</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>R$ 12,000/survey</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Low — placeholder, no repo pricing reused</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>No confirmed figure exists for the current model; needs founder input from actual quotes</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
+    <row r="8" ht="28.8" customHeight="1" s="24">
+      <c r="A8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Monthly new hectares added (base)</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>500 ha/mo, ramping +10%/mo [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">500 ha/mo, ramping +10%/mo </t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>1.75x this rate</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>0.5x this rate</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Low — placeholder ramp</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>No historical cohort exists yet to calibrate off</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
+    <row r="9" ht="28.8" customHeight="1" s="24">
+      <c r="A9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Pipeline conversion — Coplacana</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>[CONFIRM ha and probability]</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="C9" s="29" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Converts in full by M6</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Does not convert in 18mo window</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Named account, terms unconfirmed</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
+    <row r="10" ht="72" customHeight="1" s="24">
+      <c r="A10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Pipeline conversion — Thales (~30,000 ha cacao, Bahia, 200+ producers) + unnamed global trading/barter manager (deck's combined figure: 35,000 ha)</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>20% converts by M12 [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20% converts by M12 </t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>60% converts by M9</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>5% converts (consultant relationship stalls)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Consultant relationship, not direct producer — conversion probability especially uncertain; see Pipeline tab for the two-contact reconciliation</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
+    <row r="11" ht="43.2" customHeight="1" s="24">
+      <c r="A11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Gross margin — subscription</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>80% [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="C11" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>70%</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Subscription COGS = data/API/cloud costs, low marginal cost per hectare once pipeline exists</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
+    <row r="12" ht="57.6" customHeight="1" s="24">
+      <c r="A12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Gross margin — survey services</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>55% [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="C12" s="28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>45%</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Placeholder; needs real COGS build (pilot cost, processing, travel) once model isn't reusing the old per-ha cost table</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
+    <row r="13" ht="28.8" customHeight="1" s="24">
+      <c r="A13" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Monthly churn (subscription)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>2%/mo [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2%/mo </t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>1%/mo</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>5%/mo</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>No renewal cohort exists yet to measure</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="n">
+    <row r="14" ht="28.8" customHeight="1" s="24">
+      <c r="A14" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Team headcount growth</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Per Hiring Plan: CTO M1-2, data engineer M3-4, sales M4-6 [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per Hiring Plan: CTO M1-2, data engineer M3-4, sales M4-6 </t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Same, faster ramp</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>CTO hire delayed to M4</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Sequencing confirmed by founder; exact timing not yet</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
+    <row r="15" ht="28.8" customHeight="1" s="24">
+      <c r="A15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Founder/existing team comp</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>[CONFIRM monthly pro-labore/salary for Amgad, Diana, Lucas]</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>Monthly pro-labore/salary for Amgad, Diana, Lucas</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Not yet provided</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="n">
+    <row r="16" ht="57.6" customHeight="1" s="24">
+      <c r="A16" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Base-case driver for the deck's official 2027-2029 forecast</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>~8 cooperativas (cooperative-scale accounts) by 2028, at US$0.80/ha</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>More/larger accounts, faster</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Fewer/smaller accounts, slower</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>Low — deck's own stated assumption, not independently modeled bottom-up</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Directly from the deck's revenue-scenario slide footnote; see 'Scenarios (Deck)' tab</t>
         </is>
@@ -2589,6 +6297,7 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2599,164 +6308,129 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="65.5546875" bestFit="1" customWidth="1" style="24" min="1" max="1"/>
+    <col width="20" customWidth="1" style="24" min="2" max="2"/>
+    <col width="11.88671875" bestFit="1" customWidth="1" style="24" min="3" max="3"/>
+    <col width="16" customWidth="1" style="24" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22.05" customHeight="1" s="24">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Scenarios — Official Forecast (from the Pitch Deck)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>This is the founder's own stated forecast, taken verbatim from the pitch deck's 'Receita projetada em três cenários' slide (AgrosTech_Pitch_Narrativo.pdf, 2026-09-24). LEAD WITH THIS TAB in investor conversations — the 'Budget (Base)' / 'Scenarios (Bottom-Up)' tabs are a separate, independently-built bottom-up model on a different time basis (rolling 18mo from raise-close), kept as a supporting sanity check, not a competing forecast.</t>
-        </is>
-      </c>
+      <c r="A3" s="21" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Basis (per the deck's own footnote)</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>US$ 0.80/ha and ~8 cooperativas (cooperative-scale accounts) in 2028. Projections, not results.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Pessimista (US$M)</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>Base (US$M)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>Otimista (US$M)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>2027</v>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="6" t="n">
         <v>0.18</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" t="n">
         <v>0.38</v>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="6" t="n">
         <v>0.58</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>2028</v>
       </c>
-      <c r="B9" s="8" t="n">
+      <c r="B9" s="6" t="n">
         <v>0.66</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" t="n">
         <v>1.32</v>
       </c>
-      <c r="D9" s="8" t="n">
+      <c r="D9" s="6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>2029</v>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="6" t="n">
         <v>1.6</v>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C10" t="n">
         <v>3.5</v>
       </c>
-      <c r="D10" s="8" t="n">
+      <c r="D10" s="6" t="n">
         <v>4.56</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>Implied CAGR 2027→2029 (Base)</t>
         </is>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="5">
         <f>(C10/C8)^(1/2)-1</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Cross-check vs. the 36-month (~2029) target on the deck's market slide</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Deck's stated 36-month target (US$M, from 'O Mercado' slide)</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n">
-        <v>3</v>
-      </c>
+      <c r="A14" s="1" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>This tab's 2029 Base case (US$M)</t>
-        </is>
-      </c>
-      <c r="B16" s="10">
-        <f>C10</f>
-        <v/>
-      </c>
+      <c r="B16" s="6" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Difference</t>
-        </is>
-      </c>
-      <c r="B17" s="10">
-        <f>B16-B15</f>
-        <v/>
-      </c>
+      <c r="B17" s="6" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>The 36-month target (US$3M, stated on the market-sizing slide) and the 2029 Base-case revenue projection (US$3.50M, stated on the scenarios slide) are close but not identical — both are the founder's own numbers from two different slides of the same deck, not a discrepancy this data room introduced. Worth a quick founder gut-check on which framing to lead with (a single target figure vs. the full scenario table), but not a red flag requiring reconciliation.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A3:F3"/>
+  <mergeCells count="3">
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:F5"/>
@@ -2772,184 +6446,193 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="46.77734375" bestFit="1" customWidth="1" style="24" min="1" max="1"/>
+    <col width="96.88671875" bestFit="1" customWidth="1" style="24" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22.05" customHeight="1" s="24">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Unit Economics</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Built fresh for the US$0.80/ha/year (≈R$4) subscription + survey-services model, confirmed by the founder and the pitch deck. Does not reuse knowledge-base/UNIT_ECONOMICS.md, which priced full drone missions per hectare under a different business model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="3" ht="28.05" customHeight="1" s="24">
+      <c r="A3" s="21" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="24">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Subscription (Passaporte de Crédito Rural)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Price per ha/year (US$)</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Gross margin %  [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="n">
-        <v>0.8</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gross margin % </t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Gross profit per ha/year</t>
         </is>
       </c>
-      <c r="B8" s="11">
+      <c r="B8">
         <f>B6*B7</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Avg. hectares per customer  [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="n">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avg. hectares per customer  </t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>1500</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>Annual revenue per customer</t>
         </is>
       </c>
-      <c r="B10" s="11">
+      <c r="B10">
         <f>B6*B9</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>Annual gross profit per customer</t>
         </is>
       </c>
-      <c r="B11" s="11">
+      <c r="B11">
         <f>B7*B10</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Monthly churn  [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monthly churn  </t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>0.02</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>Implied avg. customer lifetime (months)</t>
         </is>
       </c>
-      <c r="B13" s="14">
+      <c r="B13">
         <f>1/B12</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>LTV (gross profit basis)</t>
         </is>
       </c>
-      <c r="B14" s="11">
+      <c r="B14">
         <f>B11/12*B13</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="16" ht="18" customHeight="1" s="24">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>Survey services (one-off)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Avg. fee per survey (US$)  [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="n">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avg. fee per survey (US$)  </t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>3000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Gross margin %  [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="n">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gross margin %  </t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>0.55</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>Gross profit per survey</t>
         </is>
       </c>
-      <c r="B19" s="11">
+      <c r="B19">
         <f>B17*B18</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="21" ht="18" customHeight="1" s="24">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>CAC (placeholder — [CONFIRM])</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Estimated CAC per subscription customer  [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM — no paid acquisition spend to date; pipeline so far is founder-led relationship sales (Coplacana, Thales)]</t>
-        </is>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Estimated CAC per subscription customer</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>LTV : CAC ratio</t>
+        </is>
+      </c>
+      <c r="B24" s="32">
+        <f>B14/B22</f>
+        <v/>
+      </c>
+      <c r="C24" s="33">
+        <f>IF(B24&lt;1,"CAC EXCEEDS LTV — losing money per customer at these assumptions",IF(B24&lt;3,"Below the ~3x healthy-SaaS benchmark","Healthy"))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2961,6 +6644,7 @@
     <mergeCell ref="A5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2970,64 +6654,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="46" bestFit="1" customWidth="1" style="24" min="1" max="1"/>
+    <col width="21.44140625" customWidth="1" style="24" min="2" max="2"/>
+    <col width="64.109375" bestFit="1" customWidth="1" style="24" min="3" max="3"/>
+    <col width="16" customWidth="1" style="24" min="4" max="4"/>
+    <col width="24" customWidth="1" style="24" min="5" max="5"/>
+    <col width="30.33203125" bestFit="1" customWidth="1" style="24" min="6" max="6"/>
+    <col width="35.88671875" bestFit="1" customWidth="1" style="24" min="7" max="7"/>
+    <col width="20" customWidth="1" style="24" min="8" max="8"/>
+    <col width="46" customWidth="1" style="24" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22.05" customHeight="1" s="24">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Sales Pipeline</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Named accounts confirmed by founder 2026-09-24 and the pitch deck's traction slide. The deck's combined '35,000 ha prospected' figure is split below into two contacts (consultant + trading/barter manager) — see 06-customers/SALES_PIPELINE.md for the full reconciliation. Stage/probability/timing are [CONFIRM] placeholders feeding the Budget tab's ramp.</t>
-        </is>
-      </c>
+      <c r="A3" s="21" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>Hectares</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>Stage [CONFIRM]</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>Probability [CONFIRM]</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Target close (month #) [CONFIRM]</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>Annual subscription value (ha x US$0.80)</t>
         </is>
@@ -3044,27 +6726,26 @@
           <t>Cooperative</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="n"/>
+      <c r="C6" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Intial conversations</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="G6" s="8">
+        <f>C6*0.8</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3080,22 +6761,20 @@
       <c r="C7" t="n">
         <v>30000</v>
       </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM — 20% used as base case, see Hypotheses]</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-      <c r="G7" s="17">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Expressed interest</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="G7" s="8">
         <f>C7*0.8</f>
         <v/>
       </c>
@@ -3111,27 +6790,26 @@
           <t>Consultant / channel</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM — deck implies ~5,000 ha to reach the combined 35,000 ha total]</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="n"/>
+      <c r="C8" t="n">
+        <v>500000</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Case study</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="G8" s="8">
+        <f>C8*0.8</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3139,49 +6817,67 @@
           <t>[Other pipeline accounts]</t>
         </is>
       </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="n"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bradesco, itau </t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Intial conversations</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="G9" s="8">
+        <f>C9*0.8</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Total (named pipeline, illustrative)</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n"/>
-      <c r="C10" s="20">
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="11">
         <f>SUM(C6:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="19" t="n"/>
-      <c r="E10" s="19" t="n"/>
-      <c r="F10" s="19" t="n"/>
-      <c r="G10" s="21">
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="12">
         <f>SUM(G6:G9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>Cross-check: pipeline annual value vs. deck's own 2029 Base case (Scenarios (Deck)!C10, US$M)</t>
+        </is>
+      </c>
+      <c r="G12" s="35">
+        <f>G10/1000000</f>
+        <v/>
+      </c>
+      <c r="H12" s="35">
+        <f>'Scenarios (Deck)'!C10</f>
+        <v/>
+      </c>
+      <c r="I12" s="33">
+        <f>IF(G12&gt;H12,"Pipeline alone exceeds the deck's entire 2029 target — check for a units/scale error in Hectares (col C)","OK")</f>
         <v/>
       </c>
     </row>
@@ -3191,6 +6887,7 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -3201,77 +6898,71 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="31.5546875" customWidth="1" style="24" min="1" max="1"/>
+    <col width="24" customWidth="1" style="24" min="2" max="2"/>
+    <col width="34" customWidth="1" style="24" min="3" max="3"/>
+    <col width="16" customWidth="1" style="24" min="4" max="4"/>
+    <col width="12" customWidth="1" style="24" min="5" max="5"/>
+    <col width="16" customWidth="1" style="24" min="6" max="6"/>
+    <col width="68.88671875" bestFit="1" customWidth="1" style="24" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22.05" customHeight="1" s="24">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Actuals to Date</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Revenue delivered/paid to date. Per the founder and the deck's traction slide: the 220ha CAR/SICAR georeferencing survey (Minas Gerais, likely = client 'Fabio' — link marked [CONFIRM]) and the 35ha weed-stress scan are the two confirmed engagements. Amounts are [CONFIRM] pending founder figures.</t>
-        </is>
-      </c>
+      <c r="A3" s="21" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>Engagement</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>Hectares</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Amount (US$)</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM date]</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>Fabio [CONFIRM link to deck's 220ha project]</t>
+      <c r="A6" s="45" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fabio </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3287,10 +6978,8 @@
       <c r="E6" t="n">
         <v>220</v>
       </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
+      <c r="F6" t="n">
+        <v>1400</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -3299,14 +6988,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM date]</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM client]</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3322,37 +7011,35 @@
       <c r="E7" t="n">
         <v>35</v>
       </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
+      <c r="F7" t="n">
+        <v>180</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Delivered &amp; paid — generated retention and scope renegotiation (per deck)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Total revenue to date</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n"/>
-      <c r="C8" s="19" t="n"/>
-      <c r="D8" s="19" t="n"/>
-      <c r="E8" s="19" t="n"/>
-      <c r="F8" s="21">
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="12">
         <f>SUM(F6:F7)</f>
         <v/>
       </c>
-      <c r="G8" s="19" t="n"/>
+      <c r="G8" s="10" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
-        <is>
-          <t>Cash &amp; burn to date  [CONFIRM]</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cash &amp; burn to date </t>
         </is>
       </c>
     </row>
@@ -3362,10 +7049,8 @@
           <t>Cash in bank today</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
+      <c r="B11" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -3374,30 +7059,27 @@
           <t>Avg. monthly burn to date</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
+      <c r="B12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>Runway at current burn (months)</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>[CONFIRM]</t>
-        </is>
+      <c r="B13" s="46">
+        <f>B11/B12</f>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:H3"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -3408,147 +7090,127 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:T30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="86.44140625" bestFit="1" customWidth="1" style="24" min="1" max="1"/>
+    <col width="11" customWidth="1" style="24" min="2" max="16"/>
+    <col width="20.109375" bestFit="1" customWidth="1" style="24" min="17" max="19"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>18-Month Budget — Bottom-Up Build (Supporting)</t>
+    <row r="1" ht="22.05" customHeight="1" s="24">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-Month Budget — Bottom-Up Build </t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>SUPPORTING MODEL, not the official forecast — see the 'Scenarios (Deck)' tab for that. This is an independent bottom-up build (named pipeline x unit economics x cost assumptions), useful for burn/runway planning. Figures are in US$. All driver assumptions live in green cells. Change these, not the formula rows, to adjust the model. Months are relative (M1 = first full month post-close), which is a different time basis than the deck's calendar-year scenarios — the two are not expected to match exactly.</t>
-        </is>
-      </c>
+      <c r="A3" s="21" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Driver / Line item</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="G5" s="23" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>M6</t>
         </is>
       </c>
-      <c r="H5" s="23" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>M7</t>
         </is>
       </c>
-      <c r="I5" s="23" t="inlineStr">
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>M8</t>
         </is>
       </c>
-      <c r="J5" s="23" t="inlineStr">
+      <c r="J5" s="13" t="inlineStr">
         <is>
           <t>M9</t>
         </is>
       </c>
-      <c r="K5" s="23" t="inlineStr">
+      <c r="K5" s="13" t="inlineStr">
         <is>
           <t>M10</t>
         </is>
       </c>
-      <c r="L5" s="23" t="inlineStr">
+      <c r="L5" s="13" t="inlineStr">
         <is>
           <t>M11</t>
         </is>
       </c>
-      <c r="M5" s="23" t="inlineStr">
+      <c r="M5" s="13" t="inlineStr">
         <is>
           <t>M12</t>
         </is>
       </c>
-      <c r="N5" s="23" t="inlineStr">
+      <c r="N5" s="13" t="inlineStr">
         <is>
           <t>M13</t>
         </is>
       </c>
-      <c r="O5" s="23" t="inlineStr">
+      <c r="O5" s="13" t="inlineStr">
         <is>
           <t>M14</t>
         </is>
       </c>
-      <c r="P5" s="23" t="inlineStr">
+      <c r="P5" s="13" t="inlineStr">
         <is>
           <t>M15</t>
         </is>
       </c>
-      <c r="Q5" s="23" t="inlineStr">
+      <c r="Q5" s="13" t="inlineStr">
         <is>
           <t>M16</t>
         </is>
       </c>
-      <c r="R5" s="23" t="inlineStr">
+      <c r="R5" s="13" t="inlineStr">
         <is>
           <t>M17</t>
         </is>
       </c>
-      <c r="S5" s="23" t="inlineStr">
+      <c r="S5" s="13" t="inlineStr">
         <is>
           <t>M18</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Cumulative hectares under subscription</t>
         </is>
       </c>
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="14" t="n">
         <v>500</v>
       </c>
       <c r="C6">
@@ -3621,1094 +7283,1094 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>New surveys delivered this month  [CONFIRM ramp]</t>
-        </is>
-      </c>
-      <c r="B7" s="24">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New surveys delivered this month </t>
+        </is>
+      </c>
+      <c r="B7" s="14">
         <f>ROUND(2+(1-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="14">
         <f>ROUND(2+(2-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="14">
         <f>ROUND(2+(3-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="14">
         <f>ROUND(2+(4-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="14">
         <f>ROUND(2+(5-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="14">
         <f>ROUND(2+(6-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="14">
         <f>ROUND(2+(7-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="14">
         <f>ROUND(2+(8-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="14">
         <f>ROUND(2+(9-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="K7" s="24">
+      <c r="K7" s="14">
         <f>ROUND(2+(10-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="L7" s="24">
+      <c r="L7" s="14">
         <f>ROUND(2+(11-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="M7" s="24">
+      <c r="M7" s="14">
         <f>ROUND(2+(12-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="N7" s="24">
+      <c r="N7" s="14">
         <f>ROUND(2+(13-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="O7" s="24">
+      <c r="O7" s="14">
         <f>ROUND(2+(14-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="P7" s="24">
+      <c r="P7" s="14">
         <f>ROUND(2+(15-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="Q7" s="24">
+      <c r="Q7" s="14">
         <f>ROUND(2+(16-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="R7" s="24">
+      <c r="R7" s="14">
         <f>ROUND(2+(17-1)*0.24,0)</f>
         <v/>
       </c>
-      <c r="S7" s="24">
+      <c r="S7" s="14">
         <f>ROUND(2+(18-1)*0.24,0)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="18" customHeight="1" s="24">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>Subscription revenue (monthly recognition of US$0.80/ha/yr)</t>
         </is>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="8">
         <f>B6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="8">
         <f>C6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="8">
         <f>D6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="8">
         <f>E6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="8">
         <f>F6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="8">
         <f>G6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="8">
         <f>H6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="8">
         <f>I6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="8">
         <f>J6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="K10" s="17">
+      <c r="K10" s="8">
         <f>K6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="L10" s="17">
+      <c r="L10" s="8">
         <f>L6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="M10" s="17">
+      <c r="M10" s="8">
         <f>M6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="N10" s="17">
+      <c r="N10" s="8">
         <f>N6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="O10" s="17">
+      <c r="O10" s="8">
         <f>O6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="P10" s="17">
+      <c r="P10" s="8">
         <f>P6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="Q10" s="17">
+      <c r="Q10" s="8">
         <f>Q6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="R10" s="17">
+      <c r="R10" s="8">
         <f>R6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
-      <c r="S10" s="17">
+      <c r="S10" s="8">
         <f>S6*'Unit Economics'!$B$6/12</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>Survey services revenue</t>
         </is>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="8">
         <f>B7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="8">
         <f>C7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="8">
         <f>D7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="8">
         <f>E7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="8">
         <f>F7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="8">
         <f>G7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="8">
         <f>H7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="8">
         <f>I7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="8">
         <f>J7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="K11" s="17">
+      <c r="K11" s="8">
         <f>K7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="L11" s="17">
+      <c r="L11" s="8">
         <f>L7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="M11" s="17">
+      <c r="M11" s="8">
         <f>M7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="N11" s="17">
+      <c r="N11" s="8">
         <f>N7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="O11" s="17">
+      <c r="O11" s="8">
         <f>O7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="P11" s="17">
+      <c r="P11" s="8">
         <f>P7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="Q11" s="17">
+      <c r="Q11" s="8">
         <f>Q7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="R11" s="17">
+      <c r="R11" s="8">
         <f>R7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
-      <c r="S11" s="17">
+      <c r="S11" s="8">
         <f>S7*'Unit Economics'!$B$17</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>TOTAL REVENUE</t>
         </is>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="15">
         <f>B10+B11</f>
         <v/>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="15">
         <f>C10+C11</f>
         <v/>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="15">
         <f>D10+D11</f>
         <v/>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="15">
         <f>E10+E11</f>
         <v/>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="15">
         <f>F10+F11</f>
         <v/>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="15">
         <f>G10+G11</f>
         <v/>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="15">
         <f>H10+H11</f>
         <v/>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="15">
         <f>I10+I11</f>
         <v/>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="15">
         <f>J10+J11</f>
         <v/>
       </c>
-      <c r="K12" s="25">
+      <c r="K12" s="15">
         <f>K10+K11</f>
         <v/>
       </c>
-      <c r="L12" s="25">
+      <c r="L12" s="15">
         <f>L10+L11</f>
         <v/>
       </c>
-      <c r="M12" s="25">
+      <c r="M12" s="15">
         <f>M10+M11</f>
         <v/>
       </c>
-      <c r="N12" s="25">
+      <c r="N12" s="15">
         <f>N10+N11</f>
         <v/>
       </c>
-      <c r="O12" s="25">
+      <c r="O12" s="15">
         <f>O10+O11</f>
         <v/>
       </c>
-      <c r="P12" s="25">
+      <c r="P12" s="15">
         <f>P10+P11</f>
         <v/>
       </c>
-      <c r="Q12" s="25">
+      <c r="Q12" s="15">
         <f>Q10+Q11</f>
         <v/>
       </c>
-      <c r="R12" s="25">
+      <c r="R12" s="15">
         <f>R10+R11</f>
         <v/>
       </c>
-      <c r="S12" s="25">
+      <c r="S12" s="15">
         <f>S10+S11</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="14" ht="18" customHeight="1" s="24">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>Gross profit</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="8">
         <f>B10*'Unit Economics'!$B$7+B11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="8">
         <f>C10*'Unit Economics'!$B$7+C11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="8">
         <f>D10*'Unit Economics'!$B$7+D11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="8">
         <f>E10*'Unit Economics'!$B$7+E11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="8">
         <f>F10*'Unit Economics'!$B$7+F11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="8">
         <f>G10*'Unit Economics'!$B$7+G11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="8">
         <f>H10*'Unit Economics'!$B$7+H11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="8">
         <f>I10*'Unit Economics'!$B$7+I11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="J15" s="17">
+      <c r="J15" s="8">
         <f>J10*'Unit Economics'!$B$7+J11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="8">
         <f>K10*'Unit Economics'!$B$7+K11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="L15" s="17">
+      <c r="L15" s="8">
         <f>L10*'Unit Economics'!$B$7+L11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="M15" s="17">
+      <c r="M15" s="8">
         <f>M10*'Unit Economics'!$B$7+M11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="N15" s="17">
+      <c r="N15" s="8">
         <f>N10*'Unit Economics'!$B$7+N11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="8">
         <f>O10*'Unit Economics'!$B$7+O11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="P15" s="17">
+      <c r="P15" s="8">
         <f>P10*'Unit Economics'!$B$7+P11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="Q15" s="17">
+      <c r="Q15" s="8">
         <f>Q10*'Unit Economics'!$B$7+Q11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="R15" s="17">
+      <c r="R15" s="8">
         <f>R10*'Unit Economics'!$B$7+R11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
-      <c r="S15" s="17">
+      <c r="S15" s="8">
         <f>S10*'Unit Economics'!$B$7+S11*'Unit Economics'!$B$18</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="17" ht="18" customHeight="1" s="24">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>Operating costs, US$/month [CONFIRM all — placeholders below, sized against the $600K raise]</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>Founder comp (Amgad, Diana, Lucas combined), US$  [CONFIRM]</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B18" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="G18" s="11" t="n">
+      <c r="G18" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="H18" s="11" t="n">
+      <c r="H18" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="I18" s="11" t="n">
+      <c r="I18" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="J18" s="11" t="n">
+      <c r="J18" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="K18" s="11" t="n">
+      <c r="K18" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="L18" s="11" t="n">
+      <c r="L18" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="M18" s="11" t="n">
+      <c r="M18" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="N18" s="11" t="n">
+      <c r="N18" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="O18" s="11" t="n">
+      <c r="O18" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="P18" s="11" t="n">
+      <c r="P18" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="Q18" s="11" t="n">
+      <c r="Q18" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="R18" s="11" t="n">
+      <c r="R18" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="S18" s="11" t="n">
+      <c r="S18" s="7" t="n">
         <v>3000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>CTO hire (from M2), US$  [CONFIRM]</t>
         </is>
       </c>
-      <c r="B19" s="11" t="n">
+      <c r="B19" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="7" t="n">
         <v>2400</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="7" t="n">
         <v>2400</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="7" t="n">
         <v>2400</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="7" t="n">
         <v>2400</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="G19" s="7" t="n">
         <v>2400</v>
       </c>
-      <c r="H19" s="11" t="n">
+      <c r="H19" s="7" t="n">
         <v>2400</v>
       </c>
-      <c r="I19" s="11" t="n">
+      <c r="I19" s="7" t="n">
         <v>2400</v>
       </c>
-      <c r="J19" s="11" t="n">
+      <c r="J19" s="7" t="n">
         <v>2400</v>
       </c>
-      <c r="K19" s="11" t="n">
+      <c r="K19" s="7" t="n">
         <v>2400</v>
       </c>
-      <c r="L19" s="11" t="n">
+      <c r="L19" s="7" t="n">
         <v>2400</v>
       </c>
-      <c r="M19" s="11" t="n">
+      <c r="M19" s="7" t="n">
         <v>2400</v>
       </c>
-      <c r="N19" s="11" t="n">
+      <c r="N19" s="7" t="n">
         <v>2400</v>
       </c>
-      <c r="O19" s="11" t="n">
+      <c r="O19" s="7" t="n">
         <v>2400</v>
       </c>
-      <c r="P19" s="11" t="n">
+      <c r="P19" s="7" t="n">
         <v>2400</v>
       </c>
-      <c r="Q19" s="11" t="n">
+      <c r="Q19" s="7" t="n">
         <v>2400</v>
       </c>
-      <c r="R19" s="11" t="n">
+      <c r="R19" s="7" t="n">
         <v>2400</v>
       </c>
-      <c r="S19" s="11" t="n">
+      <c r="S19" s="7" t="n">
         <v>2400</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Geospatial/data engineer (from M4), US$  [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="n">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Geospatial/data engineer (from M4), US$  </t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="7" t="n">
         <v>1800</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="7" t="n">
         <v>1800</v>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="G20" s="7" t="n">
         <v>1800</v>
       </c>
-      <c r="H20" s="11" t="n">
+      <c r="H20" s="7" t="n">
         <v>1800</v>
       </c>
-      <c r="I20" s="11" t="n">
+      <c r="I20" s="7" t="n">
         <v>1800</v>
       </c>
-      <c r="J20" s="11" t="n">
+      <c r="J20" s="7" t="n">
         <v>1800</v>
       </c>
-      <c r="K20" s="11" t="n">
+      <c r="K20" s="7" t="n">
         <v>1800</v>
       </c>
-      <c r="L20" s="11" t="n">
+      <c r="L20" s="7" t="n">
         <v>1800</v>
       </c>
-      <c r="M20" s="11" t="n">
+      <c r="M20" s="7" t="n">
         <v>1800</v>
       </c>
-      <c r="N20" s="11" t="n">
+      <c r="N20" s="7" t="n">
         <v>1800</v>
       </c>
-      <c r="O20" s="11" t="n">
+      <c r="O20" s="7" t="n">
         <v>1800</v>
       </c>
-      <c r="P20" s="11" t="n">
+      <c r="P20" s="7" t="n">
         <v>1800</v>
       </c>
-      <c r="Q20" s="11" t="n">
+      <c r="Q20" s="7" t="n">
         <v>1800</v>
       </c>
-      <c r="R20" s="11" t="n">
+      <c r="R20" s="7" t="n">
         <v>1800</v>
       </c>
-      <c r="S20" s="11" t="n">
+      <c r="S20" s="7" t="n">
         <v>1800</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>Sales hire (from M5), US$  [CONFIRM]</t>
         </is>
       </c>
-      <c r="B21" s="11" t="n">
+      <c r="B21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="C21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="7" t="n">
         <v>1600</v>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="G21" s="7" t="n">
         <v>1600</v>
       </c>
-      <c r="H21" s="11" t="n">
+      <c r="H21" s="7" t="n">
         <v>1600</v>
       </c>
-      <c r="I21" s="11" t="n">
+      <c r="I21" s="7" t="n">
         <v>1600</v>
       </c>
-      <c r="J21" s="11" t="n">
+      <c r="J21" s="7" t="n">
         <v>1600</v>
       </c>
-      <c r="K21" s="11" t="n">
+      <c r="K21" s="7" t="n">
         <v>1600</v>
       </c>
-      <c r="L21" s="11" t="n">
+      <c r="L21" s="7" t="n">
         <v>1600</v>
       </c>
-      <c r="M21" s="11" t="n">
+      <c r="M21" s="7" t="n">
         <v>1600</v>
       </c>
-      <c r="N21" s="11" t="n">
+      <c r="N21" s="7" t="n">
         <v>1600</v>
       </c>
-      <c r="O21" s="11" t="n">
+      <c r="O21" s="7" t="n">
         <v>1600</v>
       </c>
-      <c r="P21" s="11" t="n">
+      <c r="P21" s="7" t="n">
         <v>1600</v>
       </c>
-      <c r="Q21" s="11" t="n">
+      <c r="Q21" s="7" t="n">
         <v>1600</v>
       </c>
-      <c r="R21" s="11" t="n">
+      <c r="R21" s="7" t="n">
         <v>1600</v>
       </c>
-      <c r="S21" s="11" t="n">
+      <c r="S21" s="7" t="n">
         <v>1600</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Data/infra (satellite APIs, cloud, MapBiomas-class data), US$  [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="n">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data/infra (satellite APIs, cloud, MapBiomas-class data), US$ </t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="C22" s="11" t="n">
+      <c r="C22" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="D22" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="G22" s="11" t="n">
+      <c r="G22" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="H22" s="11" t="n">
+      <c r="H22" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="I22" s="11" t="n">
+      <c r="I22" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="J22" s="11" t="n">
+      <c r="J22" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="K22" s="11" t="n">
+      <c r="K22" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="L22" s="11" t="n">
+      <c r="L22" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="M22" s="11" t="n">
+      <c r="M22" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="N22" s="11" t="n">
+      <c r="N22" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="O22" s="11" t="n">
+      <c r="O22" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="P22" s="11" t="n">
+      <c r="P22" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="Q22" s="11" t="n">
+      <c r="Q22" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="R22" s="11" t="n">
+      <c r="R22" s="7" t="n">
         <v>600</v>
       </c>
-      <c r="S22" s="11" t="n">
+      <c r="S22" s="7" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Legal &amp; entity setup — Delaware + Brazilian LTDA formation (front-loaded M1-M3), US$  [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="n">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Legal &amp; entity setup — Delaware + Brazilian LTDA formation (front-loaded M1-M3), US$</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
         <v>1000</v>
       </c>
-      <c r="C23" s="11" t="n">
+      <c r="C23" s="7" t="n">
         <v>1000</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="7" t="n">
         <v>1000</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="11" t="n">
+      <c r="G23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="11" t="n">
+      <c r="H23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="I23" s="11" t="n">
+      <c r="I23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="11" t="n">
+      <c r="J23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="K23" s="11" t="n">
+      <c r="K23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="L23" s="11" t="n">
+      <c r="L23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="M23" s="11" t="n">
+      <c r="M23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="N23" s="11" t="n">
+      <c r="N23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O23" s="11" t="n">
+      <c r="O23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="P23" s="11" t="n">
+      <c r="P23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" s="11" t="n">
+      <c r="Q23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="R23" s="11" t="n">
+      <c r="R23" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S23" s="11" t="n">
+      <c r="S23" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>G&amp;A / other, US$  [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="n">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G&amp;A / other, US$  </t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="C24" s="11" t="n">
+      <c r="C24" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="D24" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="G24" s="11" t="n">
+      <c r="G24" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="H24" s="11" t="n">
+      <c r="H24" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="I24" s="11" t="n">
+      <c r="I24" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="J24" s="11" t="n">
+      <c r="J24" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="K24" s="11" t="n">
+      <c r="K24" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="L24" s="11" t="n">
+      <c r="L24" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="M24" s="11" t="n">
+      <c r="M24" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="N24" s="11" t="n">
+      <c r="N24" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="O24" s="11" t="n">
+      <c r="O24" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="P24" s="11" t="n">
+      <c r="P24" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="Q24" s="11" t="n">
+      <c r="Q24" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="R24" s="11" t="n">
+      <c r="R24" s="7" t="n">
         <v>800</v>
       </c>
-      <c r="S24" s="11" t="n">
+      <c r="S24" s="7" t="n">
         <v>800</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>TOTAL OPERATING COSTS</t>
         </is>
       </c>
-      <c r="B25" s="25">
+      <c r="B25" s="15">
         <f>SUM(B18:B24)</f>
         <v/>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="15">
         <f>SUM(C18:C24)</f>
         <v/>
       </c>
-      <c r="D25" s="25">
+      <c r="D25" s="15">
         <f>SUM(D18:D24)</f>
         <v/>
       </c>
-      <c r="E25" s="25">
+      <c r="E25" s="15">
         <f>SUM(E18:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="25">
+      <c r="F25" s="15">
         <f>SUM(F18:F24)</f>
         <v/>
       </c>
-      <c r="G25" s="25">
+      <c r="G25" s="15">
         <f>SUM(G18:G24)</f>
         <v/>
       </c>
-      <c r="H25" s="25">
+      <c r="H25" s="15">
         <f>SUM(H18:H24)</f>
         <v/>
       </c>
-      <c r="I25" s="25">
+      <c r="I25" s="15">
         <f>SUM(I18:I24)</f>
         <v/>
       </c>
-      <c r="J25" s="25">
+      <c r="J25" s="15">
         <f>SUM(J18:J24)</f>
         <v/>
       </c>
-      <c r="K25" s="25">
+      <c r="K25" s="15">
         <f>SUM(K18:K24)</f>
         <v/>
       </c>
-      <c r="L25" s="25">
+      <c r="L25" s="15">
         <f>SUM(L18:L24)</f>
         <v/>
       </c>
-      <c r="M25" s="25">
+      <c r="M25" s="15">
         <f>SUM(M18:M24)</f>
         <v/>
       </c>
-      <c r="N25" s="25">
+      <c r="N25" s="15">
         <f>SUM(N18:N24)</f>
         <v/>
       </c>
-      <c r="O25" s="25">
+      <c r="O25" s="15">
         <f>SUM(O18:O24)</f>
         <v/>
       </c>
-      <c r="P25" s="25">
+      <c r="P25" s="15">
         <f>SUM(P18:P24)</f>
         <v/>
       </c>
-      <c r="Q25" s="25">
+      <c r="Q25" s="15">
         <f>SUM(Q18:Q24)</f>
         <v/>
       </c>
-      <c r="R25" s="25">
+      <c r="R25" s="15">
         <f>SUM(R18:R24)</f>
         <v/>
       </c>
-      <c r="S25" s="25">
+      <c r="S25" s="15">
         <f>SUM(S18:S24)</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="27" ht="18" customHeight="1" s="24">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>Cash flow &amp; runway</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>Net burn (gross profit − opex)</t>
         </is>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="8">
         <f>B15-B25</f>
         <v/>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="8">
         <f>C15-C25</f>
         <v/>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="8">
         <f>D15-D25</f>
         <v/>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="8">
         <f>E15-E25</f>
         <v/>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="8">
         <f>F15-F25</f>
         <v/>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="8">
         <f>G15-G25</f>
         <v/>
       </c>
-      <c r="H28" s="17">
+      <c r="H28" s="8">
         <f>H15-H25</f>
         <v/>
       </c>
-      <c r="I28" s="17">
+      <c r="I28" s="8">
         <f>I15-I25</f>
         <v/>
       </c>
-      <c r="J28" s="17">
+      <c r="J28" s="8">
         <f>J15-J25</f>
         <v/>
       </c>
-      <c r="K28" s="17">
+      <c r="K28" s="8">
         <f>K15-K25</f>
         <v/>
       </c>
-      <c r="L28" s="17">
+      <c r="L28" s="8">
         <f>L15-L25</f>
         <v/>
       </c>
-      <c r="M28" s="17">
+      <c r="M28" s="8">
         <f>M15-M25</f>
         <v/>
       </c>
-      <c r="N28" s="17">
+      <c r="N28" s="8">
         <f>N15-N25</f>
         <v/>
       </c>
-      <c r="O28" s="17">
+      <c r="O28" s="8">
         <f>O15-O25</f>
         <v/>
       </c>
-      <c r="P28" s="17">
+      <c r="P28" s="8">
         <f>P15-P25</f>
         <v/>
       </c>
-      <c r="Q28" s="17">
+      <c r="Q28" s="8">
         <f>Q15-Q25</f>
         <v/>
       </c>
-      <c r="R28" s="17">
+      <c r="R28" s="8">
         <f>R15-R25</f>
         <v/>
       </c>
-      <c r="S28" s="17">
+      <c r="S28" s="8">
         <f>S15-S25</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>Cash balance, US$ (starting: US$600,000 raise)</t>
         </is>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="8">
         <f>600000+B28</f>
         <v/>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="8">
         <f>B29+C28</f>
         <v/>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="8">
         <f>C29+D28</f>
         <v/>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="8">
         <f>D29+E28</f>
         <v/>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="8">
         <f>E29+F28</f>
         <v/>
       </c>
-      <c r="G29" s="17">
+      <c r="G29" s="8">
         <f>F29+G28</f>
         <v/>
       </c>
-      <c r="H29" s="17">
+      <c r="H29" s="8">
         <f>G29+H28</f>
         <v/>
       </c>
-      <c r="I29" s="17">
+      <c r="I29" s="8">
         <f>H29+I28</f>
         <v/>
       </c>
-      <c r="J29" s="17">
+      <c r="J29" s="8">
         <f>I29+J28</f>
         <v/>
       </c>
-      <c r="K29" s="17">
+      <c r="K29" s="8">
         <f>J29+K28</f>
         <v/>
       </c>
-      <c r="L29" s="17">
+      <c r="L29" s="8">
         <f>K29+L28</f>
         <v/>
       </c>
-      <c r="M29" s="17">
+      <c r="M29" s="8">
         <f>L29+M28</f>
         <v/>
       </c>
-      <c r="N29" s="17">
+      <c r="N29" s="8">
         <f>M29+N28</f>
         <v/>
       </c>
-      <c r="O29" s="17">
+      <c r="O29" s="8">
         <f>N29+O28</f>
         <v/>
       </c>
-      <c r="P29" s="17">
+      <c r="P29" s="8">
         <f>O29+P28</f>
         <v/>
       </c>
-      <c r="Q29" s="17">
+      <c r="Q29" s="8">
         <f>P29+Q28</f>
         <v/>
       </c>
-      <c r="R29" s="17">
+      <c r="R29" s="8">
         <f>Q29+R28</f>
         <v/>
       </c>
-      <c r="S29" s="17">
+      <c r="S29" s="8">
         <f>R29+S28</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>Runway remaining (months, at trailing burn)  [CONFIRM once burn stabilizes]</t>
         </is>
@@ -4807,68 +8469,64 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" style="24" min="1" max="1"/>
+    <col width="23.5546875" bestFit="1" customWidth="1" style="24" min="2" max="2"/>
+    <col width="23.33203125" bestFit="1" customWidth="1" style="24" min="3" max="3"/>
+    <col width="26" customWidth="1" style="24" min="4" max="4"/>
+    <col width="36.88671875" customWidth="1" style="24" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22.05" customHeight="1" s="24">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Scenarios (Bottom-Up) — Bull / Base / Bear</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>SUPPORTING sensitivity view on the bottom-up 'Budget (Base)' build — not the official forecast (see 'Scenarios (Deck)' for that). Applies multipliers to the Base case's two growth drivers (hectare growth, survey volume) from the Budget tab, per the ranges set out in Hypotheses. Figures in US$. This is a summary/comparison view, not a separately-modeled set of tabs — the Budget tab remains the single source of the base case's month-by-month detail.</t>
-        </is>
-      </c>
+      <c r="A3" s="21" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Scenario multipliers (edit these — [CONFIRM] ranges from Hypotheses tab)</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Scenario multipliers</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Hectare-growth multiplier</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>Survey-volume multiplier</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" t="n">
         <v>0.5</v>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" t="n">
         <v>0.7</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -4878,15 +8536,15 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="B8" s="24" t="n">
+      <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -4896,15 +8554,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="B9" s="24" t="n">
+      <c r="B9" t="n">
         <v>1.75</v>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C9" t="n">
         <v>1.4</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -4914,54 +8572,54 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>18-month outcomes (computed)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Month-18 hectares</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>Total 18mo revenue (US$)</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>Cash balance at M18 (US$)</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>Cash-flow positive by month?</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="16">
         <f>ROUND('Budget (Base)'!S6*B7,0)</f>
         <v/>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="8">
         <f>SUM('Budget (Base)'!B12:S12)*((B7+C7)/2)</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="8">
         <f>600000+C13-(AVERAGE('Budget (Base)'!B25:S25)*18)</f>
         <v/>
       </c>
@@ -4972,20 +8630,20 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="16">
         <f>'Budget (Base)'!S6</f>
         <v/>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="8">
         <f>SUM('Budget (Base)'!B12:S12)</f>
         <v/>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="8">
         <f>'Budget (Base)'!S29</f>
         <v/>
       </c>
@@ -4996,20 +8654,20 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="16">
         <f>ROUND('Budget (Base)'!S6*B9,0)</f>
         <v/>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="8">
         <f>SUM('Budget (Base)'!B12:S12)*((B9+C9)/2)</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="8">
         <f>600000+C15-(AVERAGE('Budget (Base)'!B25:S25)*18)</f>
         <v/>
       </c>
@@ -5020,15 +8678,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Bull/Bear revenue and cash figures are directional approximations (average scenario multiplier applied to the Base case's aggregate 18-month revenue/costs), not independently re-run month-by-month models. For a full month-by-month Bull or Bear budget, duplicate the 'Budget (Base)' tab and change its driver formulas using the multipliers above — recommended before presenting scenario detail beyond this summary.</t>
-        </is>
-      </c>
+      <c r="A17" s="21" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:F3"/>
+  <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A17:F17"/>
   </mergeCells>
@@ -5043,30 +8696,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" style="24" min="1" max="1"/>
+    <col width="24" customWidth="1" style="24" min="2" max="2"/>
+    <col width="18" customWidth="1" style="24" min="3" max="3"/>
+    <col width="34" customWidth="1" style="24" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="22.05" customHeight="1" s="24">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Cap Table</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Mirrors 04-investment-documents/CAP_TABLE.md. Raise/cap/% are confirmed by the pitch deck's ask slide. Founder split and pool size below remain illustrative placeholders — edit green cells.</t>
-        </is>
-      </c>
+      <c r="A3" s="21" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>SAFE mechanics (confirmed by pitch deck's ask slide)</t>
         </is>
@@ -5078,7 +8728,7 @@
           <t>Raise (US$)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="8" t="n">
         <v>600000</v>
       </c>
     </row>
@@ -5088,7 +8738,7 @@
           <t>Post-money valuation cap (US$)</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="8" t="n">
         <v>4000000</v>
       </c>
     </row>
@@ -5098,7 +8748,7 @@
           <t>SAFE holders' post-money %</t>
         </is>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="5">
         <f>B6/B7</f>
         <v/>
       </c>
@@ -5106,10 +8756,10 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Option pool %  [CONFIRM]</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="n">
+          <t xml:space="preserve">Option pool %  </t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5119,30 +8769,30 @@
           <t>Remaining for founders %</t>
         </is>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="5">
         <f>1-B8-B9</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>Founder split (of the 'remaining for founders' pool)  [CONFIRM — equal-thirds placeholder]</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>Pre-SAFE illustrative split</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Post-SAFE %</t>
         </is>
@@ -5154,10 +8804,10 @@
           <t>Amgad</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="C14" s="9">
+      <c r="B14" s="17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C14" s="5">
         <f>B14*$B$10</f>
         <v/>
       </c>
@@ -5168,10 +8818,10 @@
           <t>Diana Dutra</t>
         </is>
       </c>
-      <c r="B15" s="27" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="C15" s="9">
+      <c r="B15" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C15" s="5">
         <f>B15*$B$10</f>
         <v/>
       </c>
@@ -5182,53 +8832,88 @@
           <t>Lucas Costa</t>
         </is>
       </c>
-      <c r="B16" s="27" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="C16" s="9">
+      <c r="B16" s="17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C16" s="5">
         <f>B16*$B$10</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>Checksum — do B14:B16 sum to 100%?</t>
+        </is>
+      </c>
+      <c r="B17" s="5">
+        <f>SUM(B14:B16)</f>
+        <v/>
+      </c>
+      <c r="C17" s="39">
+        <f>IF(ABS(B17-1)&lt;0.0001,"OK","MISMATCH — see B18")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="33" t="inlineStr">
+        <is>
+          <t>Unallocated founder equity  [CONFIRM WITH FOUNDER — not assumed]</t>
+        </is>
+      </c>
+      <c r="B18" s="40">
+        <f>1-B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="40">
+        <f>B18*$B$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>SAFE holders (class)</t>
         </is>
       </c>
-      <c r="C17" s="9">
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="18">
         <f>B8</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Option pool</t>
         </is>
       </c>
-      <c r="C18" s="9">
+      <c r="C20" s="5">
         <f>B9</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="41" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="19" t="n"/>
-      <c r="C19" s="28">
-        <f>SUM(C14:C18)</f>
+      <c r="B21" s="42" t="n"/>
+      <c r="C21" s="43">
+        <f>SUM(C14:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="44">
+        <f>IF(ABS(C21-1)&lt;0.0001,"OK — sums to 100%","STILL BROKEN — check inputs")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:D3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>